--- a/results/Int Task Remove ACC 0.2/Rando_fi_all.xlsx
+++ b/results/Int Task Remove ACC 0.2/Rando_fi_all.xlsx
@@ -876,7 +876,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>-0.005108877721943006 +/- 0.0010223245909324488</t>
+          <t>-0.005192629815745397 +/- 0.001535201237841159</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -886,157 +886,157 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.01825795644891127 +/- 0.0017884553185982058</t>
+          <t>0.008123953098827463 +/- 0.0017786231642877082</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>-0.004941373534338311 +/- 0.0012107899744389495</t>
+          <t>-0.003308207705192634 +/- 0.0011910772741480639</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>0.00439698492462316 +/- 0.0019121356879113584</t>
+          <t>0.00020938023450586262 +/- 0.0018084441274446588</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>0.0038944723618090983 +/- 0.0011851735090523383</t>
+          <t>0.003978224455611401 +/- 0.0016460003355974627</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>0.012772194304857654 +/- 0.0019121356879113764</t>
+          <t>-0.004061976549413737 +/- 0.0017472902885280704</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.0006700167504188004 +/- 0.00020514989470543705</t>
+          <t>0.00041876046901169196 +/- 0.00018727537499998735</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.0006700167504188004 +/- 0.0015578789981355297</t>
+          <t>-0.00033500837520936686 +/- 0.0018425460636516038</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>-0.007998324958123892 +/- 0.003465606588978319</t>
+          <t>-0.008793969849246231 +/- 0.0030255262760784814</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>-0.011139028475711864 +/- 0.0034693995271705153</t>
+          <t>-0.012395309882747063 +/- 0.0032983867114765785</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>0.0030569514237856364 +/- 0.001522008529764343</t>
+          <t>-0.0042713567839196 +/- 0.002190401479166183</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>-0.009631490787269636 +/- 0.0011391516338974464</t>
+          <t>-0.0044807370184254515 +/- 0.0008793969849246228</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>-0.00929648241206026 +/- 0.0018802298425999687</t>
+          <t>-0.005318257956448924 +/- 0.0008592246452547277</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>0.021273031825795687 +/- 0.003047471591065354</t>
+          <t>0.010636515912897826 +/- 0.0023405676067809367</t>
         </is>
       </c>
       <c r="Q2" t="inlineStr">
         <is>
-          <t>-0.0015912897822445093 +/- 0.0037772101453198196</t>
+          <t>-0.016959798994974896 +/- 0.0047238334056442415</t>
         </is>
       </c>
       <c r="R2" t="inlineStr">
         <is>
-          <t>0.0007118927973200018 +/- 0.0021520377148290764</t>
+          <t>-0.0009631490787269769 +/- 0.0008991168573527569</t>
         </is>
       </c>
       <c r="S2" t="inlineStr">
         <is>
-          <t>-0.007788944723618052 +/- 0.0014409255053672548</t>
+          <t>-0.002638190954773867 +/- 0.0013895025144922074</t>
         </is>
       </c>
       <c r="T2" t="inlineStr">
         <is>
-          <t>-0.0077470686767168616 +/- 0.0014893985966313692</t>
+          <t>-0.007537688442211077 +/- 0.0018539316265643853</t>
         </is>
       </c>
       <c r="U2" t="inlineStr">
         <is>
-          <t>-0.005778894472361773 +/- 0.0010050251256281378</t>
+          <t>-0.0028056951423785503 +/- 0.0011552021963261048</t>
         </is>
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>-0.00012562814070348204 +/- 0.0003270623817381369</t>
+          <t>0.00016750418760468343 +/- 0.00033500837520936686</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-0.006574539363484034 +/- 0.0011399210710901408</t>
+          <t>-0.010259631490787258 +/- 0.001846823875309885</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>0.0015912897822446092 +/- 0.001651849491065001</t>
+          <t>0.0005025125628140503 +/- 0.0017746750502861898</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>-0.0067420435510887385 +/- 0.001248580528967812</t>
+          <t>-0.0005862646566163976 +/- 0.0011110970821961064</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>0.0023450586264657236 +/- 0.00107907024511936</t>
+          <t>-0.002303182579564489 +/- 0.0011275470701705493</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.004480737018425407 +/- 0.002102577924729157</t>
+          <t>-0.005192629815745397 +/- 0.0017487950601190313</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>-0.0008793969849245741 +/- 0.00034784857047396743</t>
+          <t>-0.00012562814070352646 +/- 0.0006225321920987616</t>
         </is>
       </c>
       <c r="AC2" t="inlineStr">
         <is>
-          <t>-0.006658291457286391 +/- 0.0023647919436340877</t>
+          <t>8.375209380233617e-05 +/- 0.0031269940875367514</t>
         </is>
       </c>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>-0.005443886097152384 +/- 0.0018727537499998261</t>
+          <t>-0.004983249581239524 +/- 0.0012344558603838809</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>0.0024288107202680488 +/- 0.0017041030108354838</t>
+          <t>0.002051926298157436 +/- 0.0013691610321835692</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>-0.0003350083752093447 +/- 0.001714362603891023</t>
+          <t>-0.0020100502512562903 +/- 0.0010887772194304983</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>-0.00020938023450584042 +/- 0.00028091306249994374</t>
+          <t>0.0008375209380234394 +/- 0.0004954840689363293</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.0002512562814070751 +/- 0.00042705356060243507</t>
+          <t>-0.000711892797319924 +/- 0.0004606365159128974</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
@@ -1046,122 +1046,122 @@
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.0002931323283082543 +/- 0.0010093777883747159</t>
+          <t>-0.005862646566164165 +/- 0.002674827373981781</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>-0.002177554438860918 +/- 0.0012251875073976358</t>
+          <t>0.0005443886097152517 +/- 0.001092796344279714</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>0.0015912897822446092 +/- 0.0003133716404332952</t>
+          <t>0.005318257956448902 +/- 0.0010602168258937999</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>-0.00016750418760465015 +/- 0.0005025125628140522</t>
+          <t>-8.375209380235837e-05 +/- 0.000670016750418749</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>-0.0012144053601339632 +/- 0.0014317689277452996</t>
+          <t>-0.005653266331658291 +/- 0.0018277347439526882</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>0.010008375209380294 +/- 0.0017909049229768057</t>
+          <t>0.001298157453936366 +/- 0.001479949501429839</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>0.0010469011725293687 +/- 0.0012873053726079815</t>
+          <t>0.0011306532663316604 +/- 0.000974012005830219</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.0014237855946398147 +/- 0.0013268827066796373</t>
+          <t>-0.006155778894472374 +/- 0.0009184134086876582</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-0.004983249581239501 +/- 0.0019770639253120286</t>
+          <t>0.003978224455611379 +/- 0.0012873053726079815</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
         <is>
-          <t>0.002805695142378606 +/- 0.0012429499229192414</t>
+          <t>-0.0021356783919598056 +/- 0.0013035496161032843</t>
         </is>
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-0.00247068676716915 +/- 0.0020209260489135075</t>
+          <t>-0.002763819095477393 +/- 0.001557878998135538</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>-0.004355108877721892 +/- 0.001855822429326673</t>
+          <t>-0.0028056951423785616 +/- 0.000879396984924636</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>-0.0010469011725292576 +/- 0.0013665970579631952</t>
+          <t>-0.0021356783919597943 +/- 0.0008673498817926173</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>0.0034757118927973506 +/- 0.0018449238502437724</t>
+          <t>0.005988274706867669 +/- 0.0018161849616584035</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>0.0014237855946399036 +/- 0.0007537688442211069</t>
+          <t>-0.0005862646566164198 +/- 0.0005680343369451749</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>0.00041876046901178076 +/- 0.0009363768749999119</t>
+          <t>0.0028894472361808976 +/- 0.001161258343707035</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>0.01402847571189284 +/- 0.0019121356879113606</t>
+          <t>0.005778894472361818 +/- 0.001962374290428792</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>0.004438860971524317 +/- 0.0010790702451193416</t>
+          <t>-0.006616415410385257 +/- 0.0018330040727168478</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>0.003685092127303213 +/- 0.0010887772194304753</t>
+          <t>-0.0033082077051926227 +/- 0.0011460579718093693</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-0.00012562814070347095 +/- 0.0004972505061573597</t>
+          <t>-0.0011306532663316604 +/- 0.00026813753088076665</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>-0.00046063651591286 +/- 0.0006053949872194594</t>
+          <t>0.00016750418760470566 +/- 0.0009020376561364444</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>-4.1876046901168086e-05 +/- 0.00012562814070350426</t>
+          <t>8.375209380233617e-05 +/- 0.00016750418760467234</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>-0.006365159128978182 +/- 0.0012811606818072256</t>
+          <t>-0.006658291457286436 +/- 0.0016481297030280044</t>
         </is>
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>-0.0010050251256281007 +/- 0.0015578789981355165</t>
+          <t>-0.005946398659966501 +/- 0.0020837278567210587</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1171,92 +1171,92 @@
       </c>
       <c r="BI2" t="inlineStr">
         <is>
-          <t>-0.0002931323283081544 +/- 0.0006500910676825717</t>
+          <t>-0.00046063651591290446 +/- 0.0005757004641904236</t>
         </is>
       </c>
       <c r="BJ2" t="inlineStr">
         <is>
-          <t>0.002261306532663365 +/- 0.001391394281895833</t>
+          <t>-0.0009631490787269769 +/- 0.0008592246452547571</t>
         </is>
       </c>
       <c r="BK2" t="inlineStr">
         <is>
-          <t>0.0015494137353434523 +/- 0.0022632444081862064</t>
+          <t>-0.0027219430485762143 +/- 0.0005695758169487253</t>
         </is>
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>0.0017587939698492816 +/- 0.0008743975300595131</t>
+          <t>0.0 +/- 0.0008375209380234561</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>0.001884422110552797 +/- 0.001245768407089072</t>
+          <t>-0.0021775544388609736 +/- 0.0013082495269525233</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>-0.006197654941373476 +/- 0.0016937812743849801</t>
+          <t>-0.012562814070351758 +/- 0.0017467884099341866</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>-0.01063651591289776 +/- 0.001300182135365154</t>
+          <t>0.0014656616415410495 +/- 0.0009595007736507177</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>0.002847571189279785 +/- 0.0010725501235230909</t>
+          <t>0.0072026800670016876 +/- 0.000913627480287748</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>0.00041876046901176964 +/- 0.00026484737522348934</t>
+          <t>-0.0006700167504187671 +/- 0.00046631192318511225</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>0.009128978224455653 +/- 0.0017245611626443785</t>
+          <t>0.00996649916247907 +/- 0.0022379211416897</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>-0.0006700167504187116 +/- 0.0011725293132328206</t>
+          <t>0.0074958123953098865 +/- 0.0012485805289677871</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.000879396984924663 +/- 0.001234455860383896</t>
+          <t>0.0005443886097152517 +/- 0.0009558385435940778</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>0.001256281407035209 +/- 0.002456093517355964</t>
+          <t>0.005485762144053619 +/- 0.0016050056864938716</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>0.01005025125628145 +/- 0.001388871352745122</t>
+          <t>-0.002386934673366836 +/- 0.0012845780276531042</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
         <is>
-          <t>-0.00046063651591283784 +/- 0.0016587355377167701</t>
+          <t>0.004020100502512558 +/- 0.0025209241111042585</t>
         </is>
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>4.1876046901179186e-05 +/- 0.00012562814070353758</t>
+          <t>0.00020938023450584042 +/- 0.00020938023450584045</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>0.0008375209380234949 +/- 0.0008582035817386716</t>
+          <t>-8.375209380234727e-05 +/- 0.0007204627526836302</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>0.00020938023450588482 +/- 0.00038607807610104933</t>
+          <t>-8.375209380234727e-05 +/- 0.0009695005781231314</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="CB2" t="inlineStr">
         <is>
-          <t>0.00862646566164158 +/- 0.0012729216209020709</t>
+          <t>-0.0009631490787269769 +/- 0.0015785658982387606</t>
         </is>
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>-0.001465661641541005 +/- 0.001656619802751475</t>
+          <t>0.004815745393634841 +/- 0.0009953822716921796</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
@@ -1281,37 +1281,37 @@
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>0.0002931323283082432 +/- 0.0009740120058302311</t>
+          <t>-0.004815745393634852 +/- 0.0005995737463683589</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>0.0036850921273032357 +/- 0.0013478623902371109</t>
+          <t>0.0020519262981574583 +/- 0.0007118927973199228</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>0.0013819095477387467 +/- 0.0015220085297643479</t>
+          <t>-0.0015075376884422288 +/- 0.001748795060119027</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
         <is>
-          <t>0.003433835845896216 +/- 0.0013082495269525424</t>
+          <t>-0.0006281407035175657 +/- 0.0013793692706868129</t>
         </is>
       </c>
       <c r="CI2" t="inlineStr">
         <is>
-          <t>0.005276381909547767 +/- 0.001046063316314636</t>
+          <t>-0.0010050251256281562 +/- 0.0013136002630953136</t>
         </is>
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>0.017629815745393664 +/- 0.0019502732030477466</t>
+          <t>0.0077051926298157495 +/- 0.002061730925475904</t>
         </is>
       </c>
       <c r="CK2" t="inlineStr">
         <is>
-          <t>0.0012981574539363883 +/- 0.0009988995344955274</t>
+          <t>-0.000670016750418756 +/- 0.0009585865278274197</t>
         </is>
       </c>
     </row>
@@ -1321,7 +1321,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>0.00215410107705053 +/- 0.0009767875826471905</t>
+          <t>0.000745650372825224 +/- 0.0018414341980855708</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -1331,157 +1331,157 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>-0.006255178127589034 +/- 0.0013919053534723611</t>
+          <t>-0.01151615575807785 +/- 0.0013714122085539877</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>-0.004142502071251009 +/- 0.001925260984030222</t>
+          <t>-0.009817729908864935 +/- 0.002533708149688979</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>-0.0007456503728251462 +/- 0.001060998216641719</t>
+          <t>-0.008077879038939506 +/- 0.0019452124079327312</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>-0.004432477216238595 +/- 0.0010487977548609803</t>
+          <t>0.0045567522783761414 +/- 0.002144520150048841</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.009237779618889807 +/- 0.0010155468659595135</t>
+          <t>-0.011267605633802791 +/- 0.0016445263663031717</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.00037282518641253983 +/- 0.0001242750621375133</t>
+          <t>4.142502071251553e-05 +/- 0.0001242750621375466</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-0.006089478044739005 +/- 0.001270742473088484</t>
+          <t>-0.001822700911350439 +/- 0.002185734210152931</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0.06640430820215412 +/- 0.006277086791054743</t>
+          <t>0.06640430820215412 +/- 0.006062930708596687</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>0.05472245236122619 +/- 0.003641869569854965</t>
+          <t>0.04610604805302404 +/- 0.004556940570034586</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>0.0005799502899751618 +/- 0.0010180783535579411</t>
+          <t>-0.005509527754763854 +/- 0.0016780968600272367</t>
         </is>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>-0.0037696768848384356 +/- 0.0013416847341094955</t>
+          <t>-0.0016984258492129146 +/- 0.0024044360995743945</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>0.0008699254349627372 +/- 0.001148751004462463</t>
+          <t>0.0033140016570008535 +/- 0.0018525832456502138</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>0.04212924606462306 +/- 0.0037192656131363063</t>
+          <t>0.027796188898094466 +/- 0.0040817836786237035</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>0.017564208782104396 +/- 0.0036122998105371476</t>
+          <t>0.011847555923777963 +/- 0.0030899844571618046</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
         <is>
-          <t>-0.01101905550952773 +/- 0.0013638838138487566</t>
+          <t>-0.003811101905550929 +/- 0.001869182133003897</t>
         </is>
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0.000497100248550153 +/- 0.0012808305578906386</t>
+          <t>-0.003189726594863285 +/- 0.002429993268610204</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.0003314001657001131 +/- 0.0013588417122499185</t>
+          <t>0.005053852526926273 +/- 0.002928019394709595</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>0.001988400994200501 +/- 0.0008032609540043461</t>
+          <t>-0.003935376967688487 +/- 0.0013645127665286385</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0.00041425020712513303 +/- 0.0002619948351423654</t>
+          <t>8.285004142504216e-05 +/- 0.00024855012427507097</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>0.00907207953603979 +/- 0.003178948640091075</t>
+          <t>-0.002609776304888123 +/- 0.0024650498006316304</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>-0.0012841756420877814 +/- 0.0012626139730015093</t>
+          <t>-0.000994200497100206 +/- 0.001529924218112618</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>0.001988400994200523 +/- 0.0012537486288667502</t>
+          <t>0.002071251035625521 +/- 0.0018056747901991127</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>-0.0012841756420877925 +/- 0.0011782487699526023</t>
+          <t>-0.0001657000828499955 +/- 0.0015186663446415103</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.0001657000828500066 +/- 0.0014727745513364743</t>
+          <t>-0.0022369511184755276 +/- 0.0022628832284586065</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>0.00037282518641262863 +/- 0.0005056568192101677</t>
+          <t>0.0011599005799503015 +/- 0.0006628003314001693</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>0.000497100248550153 +/- 0.0022369511184755332</t>
+          <t>-0.015285832642916308 +/- 0.002937673678788944</t>
         </is>
       </c>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>-0.0022369511184755276 +/- 0.0009299894084773905</t>
+          <t>-0.0012427506213752771 +/- 0.0022613660420805716</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>-0.004059652029826 +/- 0.001479749055467407</t>
+          <t>-0.0002485501242750265 +/- 0.0014254060094519541</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-0.0015741507870753568 +/- 0.001784644509406635</t>
+          <t>-0.002361226180613052 +/- 0.002192397451930292</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>0.0005799502899751507 +/- 0.0006199929389849177</t>
+          <t>0.000497100248550153 +/- 0.0009037872505911779</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.0010356255178127882 +/- 0.0008738617692514038</t>
+          <t>-4.142502071247112e-05 +/- 0.00043248991337655997</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
@@ -1491,122 +1491,122 @@
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.0020712510356254987 +/- 0.0013863463571401355</t>
+          <t>0.0021126760563380366 +/- 0.0014163480527985709</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>0.004763877381938719 +/- 0.0018548975291829246</t>
+          <t>-0.0015741507870753568 +/- 0.0018414341980855853</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>0.000331400165700102 +/- 0.00040588065331948874</t>
+          <t>0.0006628003314001818 +/- 0.0006199929389849191</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>-4.1425020712482216e-05 +/- 0.000538525269262636</t>
+          <t>0.0006628003314001818 +/- 0.0007222699160796397</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>-0.003396851698425829 +/- 0.0018320914985497838</t>
+          <t>-0.0065451532725766095 +/- 0.0019412385275658676</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>-0.002195526097763023 +/- 0.0011427600848495354</t>
+          <t>0.0013256006628003414 +/- 0.0020612850546188363</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-0.0009942004971002284 +/- 0.0007903390235434405</t>
+          <t>0.0003728251864126175 +/- 0.0005988745772493994</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.002692626346313176 +/- 0.0006743504803686592</t>
+          <t>-0.000455675227837582 +/- 0.0016616546081301992</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-0.0017398508699253967 +/- 0.000844907955856324</t>
+          <t>0.0007870753935377173 +/- 0.0012626139730014928</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
         <is>
-          <t>-0.0023198011599005696 +/- 0.0009299894084773755</t>
+          <t>-0.0028997514498757203 +/- 0.0018983329308019169</t>
         </is>
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>0.0015327257663628857 +/- 0.0011576792553837606</t>
+          <t>0.006462303231151645 +/- 0.0023666705645543845</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>0.0022783761391880876 +/- 0.0012734404431598398</t>
+          <t>0.0012841756420878703 +/- 0.0016923527933567124</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>0.002941176470588247 +/- 0.001207025872769963</t>
+          <t>0.00849212924606465 +/- 0.0014260078275110694</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>-0.0005799502899751063 +/- 0.0010347966857329578</t>
+          <t>0.006048053024026556 +/- 0.0014958964445126526</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.00045378836578720884</t>
+          <t>0.0005385252692626463 +/- 0.0008894329143986489</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>-0.0001657000828500177 +/- 0.000768319676511655</t>
+          <t>0.0042667771333886 +/- 0.0017084996377217155</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>-0.0005799502899751175 +/- 0.0013125915093417497</t>
+          <t>0.010149130074565037 +/- 0.002452487177401108</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>0.002071251035625532 +/- 0.001767251781913955</t>
+          <t>0.00915492957746481 +/- 0.002495492209085161</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-0.003065451532725716 +/- 0.0013384833820549796</t>
+          <t>-0.008574979287489615 +/- 0.002923620544920286</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-0.000207125103562511 +/- 0.0003819198201032674</t>
+          <t>0.0009113504556752417 +/- 0.00036113495803984086</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>-0.0008285004142501662 +/- 0.0004901474551035263</t>
+          <t>0.0005799502899751507 +/- 0.0004971002485501159</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>-0.0004971002485500753 +/- 0.00016570008285006209</t>
+          <t>0.00041425020712512197 +/- 0.0004142502071251108</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>0.005758077879038948 +/- 0.0019991596540205056</t>
+          <t>-0.017067108533554254 +/- 0.001333345231104456</t>
         </is>
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>-0.005343827671913803 +/- 0.0017521363697229964</t>
+          <t>0.013711681855840952 +/- 0.002502359289235963</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1616,92 +1616,92 @@
       </c>
       <c r="BI3" t="inlineStr">
         <is>
-          <t>-0.000207125103562511 +/- 0.0004631458114125578</t>
+          <t>0.001201325600662817 +/- 0.0007957486624812927</t>
         </is>
       </c>
       <c r="BJ3" t="inlineStr">
         <is>
-          <t>0.001201325600662817 +/- 0.0009527754763877209</t>
+          <t>0.005758077879038958 +/- 0.0012626139730015015</t>
         </is>
       </c>
       <c r="BK3" t="inlineStr">
         <is>
-          <t>0.0006628003314001818 +/- 0.001034796685732938</t>
+          <t>0.0032311516155758336 +/- 0.002198260010177563</t>
         </is>
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>-4.142502071249332e-05 +/- 0.0004324899133765685</t>
+          <t>0.002941176470588225 +/- 0.000626874314433378</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>0.000579950289975173 +/- 0.0008923222547033054</t>
+          <t>0.005965202982601503 +/- 0.0016171682929530448</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>0.00352112676056342 +/- 0.0013645127665286487</t>
+          <t>0.004846727423363728 +/- 0.0023068195181981583</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>-0.0019055509527754698 +/- 0.0017398508699254438</t>
+          <t>0.00534382767191387 +/- 0.001475684600708945</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>0.005136702568351292 +/- 0.001563211455187525</t>
+          <t>0.004183927091963568 +/- 0.0016303785131859694</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>0.000331400165700102 +/- 0.00030999646949245884</t>
+          <t>-0.0007870753935376729 +/- 0.00022308056367583386</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>0.0020298260149130163 +/- 0.00098814088167992</t>
+          <t>0.0016570008285004324 +/- 0.0018245828952398666</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>-0.004225352112676051 +/- 0.0009942004971002457</t>
+          <t>0.008740679370339722 +/- 0.001732437751974025</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>-0.0006213753106876329 +/- 0.00038191982010326133</t>
+          <t>0.0004556752278376375 +/- 0.0010553222206178062</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>0.020132560066280048 +/- 0.0022552870901103995</t>
+          <t>0.02684341342170673 +/- 0.002414051745539949</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>0.004225352112676062 +/- 0.0010281419756413396</t>
+          <t>0.005468102734051394 +/- 0.001479749055467445</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
         <is>
-          <t>0.00020712510356257763 +/- 0.0009309115598278449</t>
+          <t>0.0030240265120132894 +/- 0.0014114933750953567</t>
         </is>
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>0.0001657000828500621 +/- 0.00020294032665977497</t>
+          <t>-4.142502071249332e-05 +/- 0.00034410206557241956</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>8.285004142504216e-05 +/- 0.00024855012427507097</t>
+          <t>-0.001325600662800286 +/- 0.001077050538525279</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>0.0009113504556752527 +/- 0.0006628003314001693</t>
+          <t>0.0003314001657001131 +/- 0.0005799502899751443</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="CB3" t="inlineStr">
         <is>
-          <t>0.0005385252692626574 +/- 0.0003728251864125682</t>
+          <t>-0.0012427506213752771 +/- 0.000667958388425716</t>
         </is>
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>0.001988400994200501 +/- 0.001444539832159299</t>
+          <t>0.0038111019055509622 +/- 0.0012260686484630544</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
@@ -1726,37 +1726,37 @@
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>4.4408920985006264e-17 +/- 0.0003705166491300363</t>
+          <t>-0.001325600662800308 +/- 0.0008845963754789956</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>8.285004142504216e-05 +/- 0.0006882041311448259</t>
+          <t>-0.0007456503728251462 +/- 0.0014913007456503757</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>0.0016984258492129367 +/- 0.0010222835691178838</t>
+          <t>0.004805302402651224 +/- 0.0012592116117291325</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
         <is>
-          <t>0.0021955260977630565 +/- 0.001201325600662794</t>
+          <t>0.0008285004142502105 +/- 0.0008489602954399035</t>
         </is>
       </c>
       <c r="CI3" t="inlineStr">
         <is>
-          <t>0.0012427506213753214 +/- 0.000614432351872046</t>
+          <t>0.002816901408450734 +/- 0.0016652652230523582</t>
         </is>
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>0.006545153272576665 +/- 0.0019055509527754555</t>
+          <t>-0.0035211267605633643 +/- 0.002122400738599748</t>
         </is>
       </c>
       <c r="CK3" t="inlineStr">
         <is>
-          <t>-0.00012427506213749106 +/- 0.0006692416910274836</t>
+          <t>0.003852526926263489 +/- 0.0014710257584560837</t>
         </is>
       </c>
     </row>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>0.0007350096711798537 +/- 0.0006104345778746289</t>
+          <t>-0.0003094777562862139 +/- 0.0008615496112696228</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -1776,157 +1776,157 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.0015473887814313025 +/- 0.0006700389971252739</t>
+          <t>-0.0006189555125724721 +/- 0.0008684697996380423</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.0019342359767891225 +/- 0.0005190099754351543</t>
+          <t>0.0010058027079304255 +/- 0.0005789798664253787</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>0.003945841392649874 +/- 0.001005802707930359</t>
+          <t>0.005764023210831759 +/- 0.0010005815981723486</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>0.0011605415860734825 +/- 0.0008989516470887574</t>
+          <t>0.0007736943907157179 +/- 0.0005190099754351709</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-0.00027079303675050517 +/- 0.000755095601390442</t>
+          <t>-0.0024758220502900884 +/- 0.0006519264814836817</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-3.8684719535786447e-05 +/- 0.00011605415860735935</t>
+          <t>1.1102230246251566e-17 +/- 0.0001730033251450404</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-0.0017021276595745038 +/- 0.0006285522943625496</t>
+          <t>-0.0001547388781430792 +/- 0.0008510638297872333</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>0.0027466150870405935 +/- 0.001551734709487936</t>
+          <t>-3.8684719535730935e-05 +/- 0.0013450938994749584</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
         <is>
-          <t>0.0012765957446808419 +/- 0.0013406362438037373</t>
+          <t>0.0003094777562863027 +/- 0.0008260795552828964</t>
         </is>
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>-0.0014313346228239988 +/- 0.001148226079663897</t>
+          <t>-0.000309477756286225 +/- 0.001208549272867567</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>0.0023597678916827845 +/- 0.0006800153126207797</t>
+          <t>0.0006576402321083697 +/- 0.0005484505562382184</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>-7.736943907157289e-05 +/- 0.00045113747735750606</t>
+          <t>-0.000773694390715618 +/- 0.0008475397408203595</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>0.0014313346228239765 +/- 0.0012116409874944544</t>
+          <t>0.0011992263056093354 +/- 0.0012042075370424254</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
         <is>
-          <t>-0.0022823984526112564 +/- 0.002271883459965345</t>
+          <t>0.014235976789168315 +/- 0.002081798692003662</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>0.002243713733075403 +/- 0.0005132107992813173</t>
+          <t>-0.001044487427466101 +/- 0.00034816247582204594</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>0.002669245647969032 +/- 0.0011403793402695226</t>
+          <t>-0.0006189555125724833 +/- 0.0005525283116860933</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
         <is>
-          <t>0.0008123791102514266 +/- 0.000743109195833594</t>
+          <t>0.00042553191489365095 +/- 0.000985511737164934</t>
         </is>
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-0.000154738878143168 +/- 0.0005247450663926731</t>
+          <t>0.000502901353965235 +/- 0.0008305961529432969</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>-0.00011605415860735935 +/- 0.00017727565551087837</t>
+          <t>-0.00023210831721465208 +/- 0.0001895156474106515</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>0.003133462282398436 +/- 0.0008554485256284561</t>
+          <t>0.0011992263056093244 +/- 0.0007629819312694915</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>0.0041392649903287835 +/- 0.000648474066314888</t>
+          <t>-0.002282398452611156 +/- 0.0010154278335324362</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>0.0006189555125725276 +/- 0.0006042746364337609</t>
+          <t>0.0008510638297872907 +/- 0.000618955512572529</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>0.0007736943907156512 +/- 0.00042376987041017975</t>
+          <t>0.0002321083172147409 +/- 0.0008510638297872453</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.0015473887814313136 +/- 0.0007736943907156457</t>
+          <t>0.0003868471953578756 +/- 0.0007133109831561255</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
         <is>
-          <t>0.00046421663442939296 +/- 0.00037903129482136415</t>
+          <t>-3.868471953577535e-05 +/- 0.00011605415860732604</t>
         </is>
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>-0.0010058027079303921 +/- 0.0009187111866180425</t>
+          <t>0.001818181818181852 +/- 0.0005750897000896694</t>
         </is>
       </c>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>-0.001276595744680864 +/- 0.0013517528208631363</t>
+          <t>0.004874274661508771 +/- 0.0015002490854673335</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>0.0009671179883945613 +/- 0.0016972851813137591</t>
+          <t>-0.001044487427466101 +/- 0.0012718980443151698</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-0.0031334622823984805 +/- 0.000985511737164934</t>
+          <t>-0.005725338491295873 +/- 0.0015931342577929666</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0006189555125725055 +/- 0.00035455131102171065</t>
+          <t>0.0004642166344294374 +/- 0.0003372455662314136</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.00030947775628629157 +/- 0.0002894899332127071</t>
+          <t>-0.0008510638297871909 +/- 0.0005942859379395481</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
@@ -1936,122 +1936,122 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.0007736943907156512 +/- 0.0007541040112037857</t>
+          <t>-0.0021276595744680327 +/- 0.0010558873550449684</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>-0.00301740812379111 +/- 0.001796237797484534</t>
+          <t>-0.001044487427466101 +/- 0.0014479665200938425</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>-0.0007736943907157179 +/- 0.0008114575227622127</t>
+          <t>-0.0010058027079303145 +/- 0.0003945082795816478</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>0.0006189555125725166 +/- 0.0006285522943625496</t>
+          <t>-0.00027079303675044966 +/- 0.0004908540634603206</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>0.0018181818181817854 +/- 0.0006930937279368903</t>
+          <t>0.0015473887814313914 +/- 0.001121189690227428</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>-0.00019342359767893225 +/- 0.001824754570997399</t>
+          <t>-0.000696324951644045 +/- 0.0009284332688587961</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>3.868471953577535e-05 +/- 0.00043937395325342255</t>
+          <t>-0.00011605415860730384 +/- 0.0003887766197725496</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.0002321083172146854 +/- 0.0009507315843284069</t>
+          <t>-0.0011992263056092357 +/- 0.0008377720629674181</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-7.736943907157289e-05 +/- 0.0009284332688588101</t>
+          <t>-0.003713733075435155 +/- 0.0011370938844641506</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
         <is>
-          <t>0.0009671179883945724 +/- 0.0005802707930367375</t>
+          <t>-0.0019342359767891225 +/- 0.0007133109831561435</t>
         </is>
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>0.003520309477756245 +/- 0.0011403793402695451</t>
+          <t>0.0004642166344294374 +/- 0.0005685469422320799</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>-0.004371373307543525 +/- 0.0007937440823475013</t>
+          <t>-0.00557059961315276 +/- 0.0008684697996380601</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>0.0002321083172146632 +/- 0.0006963249516441067</t>
+          <t>-0.002088974854932246 +/- 0.0007174946611602244</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>0.0030947775628626384 +/- 0.0004893272975115432</t>
+          <t>-0.001779497098645999 +/- 0.000552528311686095</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>0.001934235976789156 +/- 0.0007541040112037801</t>
+          <t>7.73694390716062e-05 +/- 0.00041664718043593456</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>0.0029400386847195257 +/- 0.0007580625896427622</t>
+          <t>0.0023984526112186154 +/- 0.000618955512572518</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>0.004564796905222412 +/- 0.0007091026220434649</t>
+          <t>0.0016247582205029532 +/- 0.0012330659536177375</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-0.005222437137330793 +/- 0.001238515326389334</t>
+          <t>-0.012301740812379081 +/- 0.0010494901327853506</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-0.0028626692456479976 +/- 0.0012853576577049207</t>
+          <t>-0.003636363636363593 +/- 0.0008510638297872363</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-0.00027079303675050517 +/- 0.00034816247582207803</t>
+          <t>-0.0005802707930367079 +/- 0.00035665549157805375</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>0.0009671179883945835 +/- 0.0004325083128626183</t>
+          <t>-0.001044487427466112 +/- 0.0002477030652778637</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
-          <t>3.868471953577535e-05 +/- 0.00032133941442623136</t>
+          <t>-0.00034816247582198924 +/- 0.00032133941442621933</t>
         </is>
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>-0.0025145067698259414 +/- 0.0015401183162394023</t>
+          <t>-0.0007350096711798316 +/- 0.0008897485493230062</t>
         </is>
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>0.0030174081237910764 +/- 0.0012208691557492734</t>
+          <t>-0.000309477756286225 +/- 0.0010351325462483276</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2061,92 +2061,92 @@
       </c>
       <c r="BI4" t="inlineStr">
         <is>
-          <t>0.001779497098645999 +/- 0.0003094777562862444</t>
+          <t>-7.73694390715285e-05 +/- 0.00028948993321265963</t>
         </is>
       </c>
       <c r="BJ4" t="inlineStr">
         <is>
-          <t>-0.002359767891682807 +/- 0.0006104345778746381</t>
+          <t>0.000232108317214752 +/- 0.0009663439842782622</t>
         </is>
       </c>
       <c r="BK4" t="inlineStr">
         <is>
-          <t>-0.0005415860735009881 +/- 0.0008855337053972723</t>
+          <t>0.0015087040618955716 +/- 0.0010300601126262624</t>
         </is>
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>0.001121856866537696 +/- 0.0010587181573233307</t>
+          <t>0.00019342359767894336 +/- 0.0003118861798181299</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>-0.003868471953578356 +/- 0.0008650166257252417</t>
+          <t>-0.0027466150870405605 +/- 0.0007823500354412801</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>-0.015125725338491314 +/- 0.0018181818181817993</t>
+          <t>-0.007272727272727231 +/- 0.0006876746164267228</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>0.001663442940038662 +/- 0.0008658812102746237</t>
+          <t>-0.0013539651837523592 +/- 0.0010271503324836909</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>0.00379110251450675 +/- 0.00048317199213912803</t>
+          <t>-0.0011218568665376737 +/- 0.0009702078300954968</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>-3.8684719535786447e-05 +/- 0.00027079303675050517</t>
+          <t>7.736943907157289e-05 +/- 0.00015473887814314579</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>-0.0005029013539652016 +/- 0.0007937440823475192</t>
+          <t>-0.00224371373307537 +/- 0.000750124542733691</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>-0.0021276595744681103 +/- 0.0006530732307982349</t>
+          <t>-0.0009671179883945392 +/- 0.0007590490085241299</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.0014700193423597407 +/- 0.0004166471804359345</t>
+          <t>0.0004255319148936731 +/- 0.000701677259079957</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>0.010367504835589935 +/- 0.0016844519193096451</t>
+          <t>0.010367504835590003 +/- 0.0011579597328507292</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>0.004526112185686615 +/- 0.0005750897000896932</t>
+          <t>0.0029787234042553457 +/- 0.0006249707706539046</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
         <is>
-          <t>0.001392649903288179 +/- 0.00043077480563482435</t>
+          <t>0.00495164410058031 +/- 0.000960129489051529</t>
         </is>
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>0.0002321083172147076 +/- 0.0002566053996406469</t>
+          <t>-0.00023210831721467428 +/- 0.00030947775628624165</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>0.00034816247582203363 +/- 0.0004393739532533981</t>
+          <t>-0.0004255319148935621 +/- 0.0004722071804925992</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>0.00023210831721469648 +/- 0.00035455131102172274</t>
+          <t>0.0010831721470019762 +/- 0.000807760658329638</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2156,52 +2156,52 @@
       </c>
       <c r="CB4" t="inlineStr">
         <is>
-          <t>-0.0005802707930367967 +/- 0.00019342359767893225</t>
+          <t>-0.0026692456479689985 +/- 0.0005854060328983191</t>
         </is>
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>-0.0007736943907156845 +/- 0.0008989516470887908</t>
+          <t>-0.001237911025145011 +/- 0.0005942859379395467</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>0.0006963249516440673 +/- 0.0001547388781431014</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>0.0007350096711798648 +/- 0.0008012501035670356</t>
+          <t>0.0002321083172147298 +/- 0.000796567128896486</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>0.0012765957446808306 +/- 0.0005750897000896865</t>
+          <t>-0.0004642166344293597 +/- 0.0009601294890515103</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>-0.0010058027079304032 +/- 0.0009663439842782898</t>
+          <t>0.0013539651837524592 +/- 0.0006297416091334534</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
         <is>
-          <t>-0.002011605415860762 +/- 0.0008440009373025628</t>
+          <t>0.001431334622824032 +/- 0.0008123791102514477</t>
         </is>
       </c>
       <c r="CI4" t="inlineStr">
         <is>
-          <t>0.0018955512572533695 +/- 0.0006576402321083207</t>
+          <t>-0.0003094777562862139 +/- 0.0009121722338531312</t>
         </is>
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>-0.003984526112185705 +/- 0.0008829951420126442</t>
+          <t>-0.005918762088974805 +/- 0.0008123791102514525</t>
         </is>
       </c>
       <c r="CK4" t="inlineStr">
         <is>
-          <t>-0.028665377176015507 +/- 0.001191715419787198</t>
+          <t>-0.010638297872340385 +/- 0.0010558873550449847</t>
         </is>
       </c>
     </row>
@@ -2211,7 +2211,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>0.002911443590780438 +/- 0.0012889104286704122</t>
+          <t>-0.0030327537403963545 +/- 0.0011184243175041784</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -2221,157 +2221,157 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>-0.005297209866558805 +/- 0.0019764414734896926</t>
+          <t>-0.00016174686615449962 +/- 0.0007278608976951404</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>0.00044480388192478235 +/- 0.0010917913465426476</t>
+          <t>-0.005822887181560899 +/- 0.0012554933033772616</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>0.0005661140315406432 +/- 0.0016789761012557</t>
+          <t>-0.000727860897695154 +/- 0.0013015347302411228</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>-0.002021835826930829 +/- 0.0012397662528714686</t>
+          <t>-0.006469874646178764 +/- 0.0010999976149401764</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>0.007238172260412479 +/- 0.0018214485450149733</t>
+          <t>0.014638091386979312 +/- 0.001886276391377349</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.000768297614233715 +/- 0.00038147922086763</t>
+          <t>-0.0003639304488475825 +/- 0.0003814792208676689</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.001374848362312986 +/- 0.001755158464554053</t>
+          <t>-0.011928831378892103 +/- 0.001890173213509128</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>2.2204460492503132e-17 +/- 0.0032500657173328046</t>
+          <t>-0.005256773150020255 +/- 0.002842100022774852</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
         <is>
-          <t>0.0071572988273352345 +/- 0.0027428496372198198</t>
+          <t>-0.006995551961180779 +/- 0.0014129725199883492</t>
         </is>
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>0.0018196522442377795 +/- 0.0013801899042358552</t>
+          <t>-0.0011726647796199586 +/- 0.0010301446989775468</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>0.001253538212697114 +/- 0.0010301446989775045</t>
+          <t>-0.0031945006065508207 +/- 0.0010141476913857097</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>-0.0010917913465426476 +/- 0.0015456138175184927</t>
+          <t>-0.000323493732308977 +/- 0.0010356852790025127</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>0.011362717347351402 +/- 0.002180960220001919</t>
+          <t>0.002183582693085273 +/- 0.0024543454760199783</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
         <is>
-          <t>-0.00537808329963606 +/- 0.0026886615786298946</t>
+          <t>-0.0033966841892438928 +/- 0.002407258563063026</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>0.0006469874646178764 +/- 0.0017364262477625424</t>
+          <t>-0.004084108370400385 +/- 0.002502180105847925</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>-0.0010109179134654145 +/- 0.0011892795123212751</t>
+          <t>-0.0022240194096240116 +/- 0.0015791042612023213</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
         <is>
-          <t>-0.007359482410028295 +/- 0.0022499680943378355</t>
+          <t>-0.007278608976951128 +/- 0.0032950341750850568</t>
         </is>
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>0.0025475131419328777 +/- 0.0009577613653317702</t>
+          <t>-0.0050545895673271835 +/- 0.0010109179134654145</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>8.087343307723316e-05 +/- 0.0001617468661544663</t>
+          <t>-0.0003639304488475714 +/- 0.0002830570157703509</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>0.022927618277395888 +/- 0.0024666397088556583</t>
+          <t>0.017266477961989435 +/- 0.0027606759706750284</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>0.001819652244237746 +/- 0.0006329347287706567</t>
+          <t>-0.0023453295592398725 +/- 0.001111825886362099</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>0.0018600889607763849 +/- 0.0014262185271774045</t>
+          <t>0.00044480388192474907 +/- 0.0015914814924508386</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>0.0008087343307723316 +/- 0.00108503096360684</t>
+          <t>0.005095026283865689 +/- 0.0016295545232195426</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.0008896077638495647 +/- 0.0012761612485288564</t>
+          <t>0.0021431459765466785 +/- 0.0014696952564000026</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>-0.0008087343307723316 +/- 0.00047845368241807885</t>
+          <t>0.00036393044884754924 +/- 0.00045927281405581927</t>
         </is>
       </c>
       <c r="AC5" t="inlineStr">
         <is>
-          <t>0.007723412858875867 +/- 0.002697162336538976</t>
+          <t>0.0022240194096239006 +/- 0.0017462857162708584</t>
         </is>
       </c>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>0.0010917913465426476 +/- 0.0011154965001321114</t>
+          <t>0.00012131014961579423 +/- 0.0015561570080787853</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>0.0015770319450060578 +/- 0.0010917913465426686</t>
+          <t>0.001536595228467419 +/- 0.0016052918108596203</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.00436716538617069 +/- 0.0010036129111193625</t>
+          <t>0.006631621512333119 +/- 0.0010419812961362694</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.00012131014961584974 +/- 0.00025892131975061754</t>
+          <t>0.0007278608976950985 +/- 0.00047156909784433726</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.00044480388192478235 +/- 0.0005256773150020155</t>
+          <t>4.043671653860548e-05 +/- 0.0004935930293463012</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
@@ -2381,122 +2381,122 @@
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.0027901334411645994 +/- 0.0009813717023463083</t>
+          <t>0.002911443590780394 +/- 0.0016154455604883088</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>0.004407602102709296 +/- 0.0013943339789378706</t>
+          <t>-4.0436716538638784e-05 +/- 0.0007334556064382355</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>-0.00036393044884754924 +/- 0.0005559129431810495</t>
+          <t>0.0008896077638495647 +/- 0.0005661140315406321</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>-8.087343307723316e-05 +/- 0.00047156909784433737</t>
+          <t>0.0008491710473109481 +/- 0.00038147922086763</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>-0.0012131014961584974 +/- 0.0015661072972937202</t>
+          <t>-0.000323493732308977 +/- 0.001806575649307644</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>0.003437120905782476 +/- 0.0014382061660961638</t>
+          <t>-0.0008087343307723982 +/- 0.0013772249386111478</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-0.0005256773150020156 +/- 0.00067784288775738</t>
+          <t>0.001455721795390197 +/- 0.0009256387498794549</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-0.0007278608976950985 +/- 0.0011264365772085687</t>
+          <t>0.0021027092600080623 +/- 0.000900568437174275</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>0.0003234937323089326 +/- 0.0011551036681832212</t>
+          <t>-0.0037606146380914527 +/- 0.0012404255277135288</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
         <is>
-          <t>0.0023857662757784228 +/- 0.0023190377612518787</t>
+          <t>-0.0009704811969268757 +/- 0.0017828878030771405</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>0.009866558835422567 +/- 0.0021715683917666825</t>
+          <t>-4.0436716538649883e-05 +/- 0.001076710631273323</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>0.004650222401941006 +/- 0.0008905263059258204</t>
+          <t>0.004124545086938891 +/- 0.0013748483623129638</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>0.0018600889607763627 +/- 0.000605201356534395</t>
+          <t>0.001738778811160513 +/- 0.0008868464294161361</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>0.005782450465022282 +/- 0.0013658993735587816</t>
+          <t>0.004973716134249839 +/- 0.0012002282312701701</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>0.00012131014961584974 +/- 0.0004063839717396187</t>
+          <t>-0.001051354630004131 +/- 0.0005178426395012576</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>0.002466639708855645 +/- 0.0013466094464494166</t>
+          <t>-0.0015770319450061354 +/- 0.0009300444803882092</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>-0.002183582693085295 +/- 0.001837091256223277</t>
+          <t>0.0011726647796198475 +/- 0.0018214485450150145</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>0.0025879498584715165 +/- 0.0024808510554271065</t>
+          <t>-0.005822887181560899 +/- 0.0019743721173851284</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-0.011686211079660313 +/- 0.002096868930443051</t>
+          <t>-0.0009704811969268423 +/- 0.0015365952284674808</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>4.043671653861658e-05 +/- 0.0005256773150020156</t>
+          <t>-0.0004852405984634545 +/- 0.0008046804990753388</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>-0.00036393044884754924 +/- 0.0006380806242644282</t>
+          <t>0.0004448038819247713 +/- 0.0007334556064382251</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
-          <t>-0.00044480388192478235 +/- 0.00033589259453772647</t>
+          <t>4.043671653861658e-05 +/- 0.00012131014961584974</t>
         </is>
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>-0.008168216740800639 +/- 0.0011830763314458637</t>
+          <t>-0.0034775576223211257 +/- 0.0017644499983236073</t>
         </is>
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>-0.00295188030731901 +/- 0.002294939526674087</t>
+          <t>-0.003437120905782498 +/- 0.002590791504996587</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2506,92 +2506,92 @@
       </c>
       <c r="BI5" t="inlineStr">
         <is>
-          <t>-0.004528912252325057 +/- 0.0010356852790024704</t>
+          <t>-0.0002021835826931384 +/- 0.0010736690697413778</t>
         </is>
       </c>
       <c r="BJ5" t="inlineStr">
         <is>
-          <t>-0.0009704811969267979 +/- 0.001057557366002577</t>
+          <t>-0.0010917913465427254 +/- 0.0010237758917244284</t>
         </is>
       </c>
       <c r="BK5" t="inlineStr">
         <is>
-          <t>0.0027092600080873552 +/- 0.0018268268496686873</t>
+          <t>-0.0026688232915487607 +/- 0.0026590023813625064</t>
         </is>
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>0.0006874241811564818 +/- 0.0005732894006776246</t>
+          <t>0.0017792155276991294 +/- 0.001057557366002577</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>0.005661140315406432 +/- 0.0007456162116694523</t>
+          <t>0.0026688232915486943 +/- 0.001924039992457772</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>-0.004650222401940929 +/- 0.0016598767288130945</t>
+          <t>-0.00307319045693496 +/- 0.0017079427482363798</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>-0.0007278608976950985 +/- 0.0012104027130687897</t>
+          <t>-0.0050950262838658 +/- 0.0021335877004889222</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>0.007723412858875877 +/- 0.0012844626101308856</t>
+          <t>0.0037606146380913417 +/- 0.0012404255277135288</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00018083849393447332</t>
+          <t>-0.00012131014961584974 +/- 0.0001853043143936832</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>0.014355034371209085 +/- 0.0018815026484645223</t>
+          <t>0.009017387788111564 +/- 0.001725563145438911</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.0038819247877072693 +/- 0.0010575573660026227</t>
+          <t>0.0005256773150019933 +/- 0.0012665151446313028</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.002304892842701156 +/- 0.000724483334701545</t>
+          <t>0.0008491710473109481 +/- 0.0004935930293462821</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>0.010877476748888004 +/- 0.0014060120218935728</t>
+          <t>0.01014961585119285 +/- 0.0019598254453785206</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>0.007359482410028329 +/- 0.0009361776710707714</t>
+          <t>0.0044076021027092075 +/- 0.001581173861384304</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
         <is>
-          <t>0.009017387788111609 +/- 0.001253538212697114</t>
+          <t>0.006227254346946954 +/- 0.0011322280630812643</t>
         </is>
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>4.043671653861658e-05 +/- 0.00021775838281983177</t>
+          <t>8.087343307723316e-05 +/- 0.00030260067826719744</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>0.0025879498584715057 +/- 0.0008326429551951021</t>
+          <t>0.0004043671653861658 +/- 0.0006520224624584273</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>-0.0008491710473109481 +/- 0.0005559129431810495</t>
+          <t>0.0008896077638495647 +/- 0.0008247504267841041</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2601,12 +2601,12 @@
       </c>
       <c r="CB5" t="inlineStr">
         <is>
-          <t>-0.000768297614233715 +/- 0.0005559129431810495</t>
+          <t>0.00028305701577031607 +/- 0.0005440203820086352</t>
         </is>
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>0.004488475535786541 +/- 0.0007767639592518764</t>
+          <t>0.0048524059846339895 +/- 0.0007672327521637707</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
@@ -2616,37 +2616,37 @@
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>0.0019409623938535959 +/- 0.0006469874646178654</t>
+          <t>0.00036393044884754924 +/- 0.00028305701577031607</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>0.0015770319450060578 +/- 0.0008375380176792724</t>
+          <t>0.00460978568540229 +/- 0.00153659522846743</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>0.005175899716943033 +/- 0.0009871860586925642</t>
+          <t>0.0064294379296400365 +/- 0.0013466094464493741</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
         <is>
-          <t>0.003234937323089393 +/- 0.0007456162116695004</t>
+          <t>0.0026283865750100777 +/- 0.0012430591305248049</t>
         </is>
       </c>
       <c r="CI5" t="inlineStr">
         <is>
-          <t>0.0008896077638495647 +/- 0.0013984323870432978</t>
+          <t>0.002304892842701145 +/- 0.0005732894006776245</t>
         </is>
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>0.014961585119288346 +/- 0.0016174686615446855</t>
+          <t>0.004933279417711223 +/- 0.0016255358869584748</t>
         </is>
       </c>
       <c r="CK5" t="inlineStr">
         <is>
-          <t>0.0020218358269308624 +/- 0.0014912324233389465</t>
+          <t>-0.0006065507480793042 +/- 0.001216466555316758</t>
         </is>
       </c>
     </row>
@@ -2656,7 +2656,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>0.0010395841663334848 +/- 0.0011477569047906812</t>
+          <t>0.0033586565373849965 +/- 0.0013641521078953938</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -2666,157 +2666,157 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>-0.00423830467812869 +/- 0.0015193922431027507</t>
+          <t>-0.0025189924030388335 +/- 0.0013740775911587084</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.010395841663334715 +/- 0.000979404135459079</t>
+          <t>0.004158336665333817 +/- 0.0009152757410843112</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.0028788484606157906 +/- 0.0019976003193597548</t>
+          <t>0.002199120351859196 +/- 0.0018169640571774148</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>0.005197920831667357 +/- 0.0012644053019465913</t>
+          <t>-0.0003998400639744548 +/- 0.0013618061867993851</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>0.0011595361855258114 +/- 0.002415312004884257</t>
+          <t>0.004918032786885196 +/- 0.0020703068318272</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.00035985605757697935 +/- 0.00011995201919232645</t>
+          <t>-0.0003598560575770016 +/- 0.00048806699783019526</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.0009996001599360648 +/- 0.0012801128023656335</t>
+          <t>0.0036385445821670802 +/- 0.0014576350366699803</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>0.005877648940423874 +/- 0.004727760045908007</t>
+          <t>0.009196321471411395 +/- 0.0031786656400402636</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
         <is>
-          <t>0.014714114354258335 +/- 0.003443270714372023</t>
+          <t>0.0051179528188723955 +/- 0.002953408286704431</t>
         </is>
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>0.000239904038384664 +/- 0.001726272142736736</t>
+          <t>0.002878848460615713 +/- 0.0014394242303078935</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>0.0017992802878848857 +/- 0.0016510054235955621</t>
+          <t>0.004278288684526144 +/- 0.0009300042662625165</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>0.0055177928828469055 +/- 0.0009256966735538226</t>
+          <t>0.010795681727309037 +/- 0.0022688941957794413</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>0.010435825669732135 +/- 0.002525331095503901</t>
+          <t>-0.004118352658936475 +/- 0.002911154202201888</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
         <is>
-          <t>-0.006197520991603311 +/- 0.0030306188823090202</t>
+          <t>-0.012315073970411872 +/- 0.0035349118121232115</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>-0.0004798080767692503 +/- 0.0014831856850053102</t>
+          <t>-0.0016793282686925926 +/- 0.0018217970011826438</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>0.0012395041983207177 +/- 0.0009020803016936011</t>
+          <t>0.0007197121151538921 +/- 0.0014394242303078706</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
         <is>
-          <t>0.0011195521791283914 +/- 0.0010240902418925024</t>
+          <t>-0.0006397441023590966 +/- 0.0011195521791283517</t>
         </is>
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>-0.001239504198320618 +/- 0.0008281613425512833</t>
+          <t>0.0039584166333466175 +/- 0.0012317410476408756</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>-0.00019992003198721076 +/- 0.00026822086895240136</t>
+          <t>0.00019992003198715524 +/- 0.0003223613653857486</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-0.014674130347860836 +/- 0.0019510392481017036</t>
+          <t>-0.011435425829668189 +/- 0.00219147374746818</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>-0.0030387844862054814 +/- 0.0012284919228898402</t>
+          <t>0.004038384646141491 +/- 0.0010341876974312167</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>-0.0051979208316672906 +/- 0.0015690857153417546</t>
+          <t>-0.00319872051179535 +/- 0.0006690603970684188</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>0.0009596161535386227 +/- 0.0010758595799339355</t>
+          <t>-0.00203918432626955 +/- 0.0005496892077116317</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.001559376249500144 +/- 0.0009703847340673104</t>
+          <t>-0.006957217113154779 +/- 0.0014102512665772353</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>-0.0005597760895641457 +/- 0.0005423694508696447</t>
+          <t>0.0002399040383845974 +/- 0.0005120451209462118</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>-0.009396241503398595 +/- 0.0026896489498348065</t>
+          <t>-0.012315073970411905 +/- 0.0028877201255926212</t>
         </is>
       </c>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>0.00187924830067977 +/- 0.0023180380712731863</t>
+          <t>-0.004198320671731326 +/- 0.0018518250582821862</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>0.0035185925629748426 +/- 0.001577215747566254</t>
+          <t>-0.0020791683326669918 +/- 0.000908262030515863</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.002159136345461854 +/- 0.0008612818563989586</t>
+          <t>0.002119152339064323 +/- 0.0012776125796617663</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.00011995201919234866 +/- 0.0007804566691700419</t>
+          <t>-3.998400639748656e-05 +/- 0.0005197920831667019</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.0016393442622950171 +/- 0.0004880669978302298</t>
+          <t>0.0003998400639743438 +/- 0.0003998400639743771</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
@@ -2826,122 +2826,122 @@
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.002159136345461865 +/- 0.0007197121151539427</t>
+          <t>0.0022391043582566383 +/- 0.0011051799249168631</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>0.00027988804478210614 +/- 0.0011456656362970436</t>
+          <t>0.00019992003198715524 +/- 0.0011622904321270287</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>-0.0009196321471411139 +/- 0.0005944049878975494</t>
+          <t>0.00019992003198715524 +/- 0.0005724838489914233</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>-0.00019992003198717744 +/- 0.0005997600959615916</t>
+          <t>0.0009996001599359538 +/- 0.0006508924668572467</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>-0.014274290283886404 +/- 0.0028162481652043675</t>
+          <t>-0.0003598560575770127 +/- 0.002065668349154653</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>0.0003198720511795594 +/- 0.001249140292028251</t>
+          <t>-0.0037984806077569376 +/- 0.0009334360279830856</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-3.998400639741995e-05 +/- 0.0006309369787308787</t>
+          <t>-0.0016393442622951282 +/- 0.0005496892077116317</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-0.002359056377448987 +/- 0.0021565432323329644</t>
+          <t>-0.0051179528188725065 +/- 0.0013942899459546488</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>0.003998400639744127 +/- 0.0013140085345985592</t>
+          <t>0.0013194722111155022 +/- 0.0014750793079325438</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
         <is>
-          <t>0.0013994402239104753 +/- 0.0011344470978897256</t>
+          <t>0.0023590563774489757 +/- 0.0008841801034584808</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>0.002718912435026011 +/- 0.0018906981875308941</t>
+          <t>0.004078368652538933 +/- 0.0015045891821052926</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>-0.00615753698520588 +/- 0.001611310810044765</t>
+          <t>-0.0046381447421032 +/- 0.0011337422533992663</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>-0.004158336665333828 +/- 0.0018685839976885963</t>
+          <t>-0.003278688524590223 +/- 0.0009082620305158219</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>-0.0027588964414233972 +/- 0.0008086264860518693</t>
+          <t>-0.007836865253898474 +/- 0.0012021828371349727</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>0.00011995201919233756 +/- 0.0006702540829364308</t>
+          <t>-0.0004798080767693391 +/- 0.0006879108570205787</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>-0.003198720511795239 +/- 0.00167742318779711</t>
+          <t>-0.00243902439024396 +/- 0.0015008656040882663</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>0.0026389444222311375 +/- 0.0017446960599177541</t>
+          <t>-0.0017592962814874547 +/- 0.001560913338340119</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-0.004038384646141491 +/- 0.002286092340491446</t>
+          <t>0.005117952818872407 +/- 0.0016172529721036747</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>0.000759696121551412 +/- 0.002388688849459229</t>
+          <t>0.0035985605757696383 +/- 0.0015993602558976138</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>0.0017193122750900013 +/- 0.0008769177208900972</t>
+          <t>7.99680127948399e-05 +/- 0.000908262030515818</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>3.9984006397464354e-05 +/- 0.00076806768141936</t>
+          <t>0.0005997600959615323 +/- 0.0004097141449803871</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.00017881391263493423</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>0.0029188324670132324 +/- 0.001012314186419191</t>
+          <t>-0.0010795681727309493 +/- 0.0021535758511787564</t>
         </is>
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>-0.0013594562175129553 +/- 0.0017262721427367446</t>
+          <t>-0.0015993602558977082 +/- 0.0015172863623358983</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2951,92 +2951,92 @@
       </c>
       <c r="BI6" t="inlineStr">
         <is>
-          <t>-0.0002399040383846196 +/- 0.0005984258115591778</t>
+          <t>0.0005197920831666814 +/- 0.000670254082936405</t>
         </is>
       </c>
       <c r="BJ6" t="inlineStr">
         <is>
-          <t>-0.0016393442622950505 +/- 0.0014576350366699842</t>
+          <t>-0.003278688524590212 +/- 0.0013827762067805342</t>
         </is>
       </c>
       <c r="BK6" t="inlineStr">
         <is>
-          <t>0.004278288684526221 +/- 0.0014198545305529595</t>
+          <t>-0.0025589764094362645 +/- 0.0018940774541906574</t>
         </is>
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>0.0011995201919232645 +/- 0.0008194282899608066</t>
+          <t>0.0003998400639743438 +/- 0.0004730971437904289</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>-0.0023190723710515447 +/- 0.0011560841499241139</t>
+          <t>-0.007317073170731747 +/- 0.0010736282752576837</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>0.002998800479808106 +/- 0.0012548864315453903</t>
+          <t>0.007676929228308616 +/- 0.002546450752193631</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>-0.0051579368252698595 +/- 0.0016721730240964832</t>
+          <t>-0.008036785285885705 +/- 0.0021713193094579026</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>-0.0006797281087564833 +/- 0.0009963963050281417</t>
+          <t>-0.0005997600959616545 +/- 0.0008985287906535035</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>0.0004398240703718637 +/- 0.0004880669978302298</t>
+          <t>-3.9984006397453255e-05 +/- 0.00021532046409972365</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>-0.003958416633346629 +/- 0.0008841801034584341</t>
+          <t>-0.004438224710116012 +/- 0.001844905556986684</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.003038784486205548 +/- 0.0014548904757025313</t>
+          <t>-0.0022790883646541917 +/- 0.001186791049952499</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>-3.998400639740884e-05 +/- 0.0007469628825377364</t>
+          <t>-0.0009196321471411695 +/- 0.00040183429112839554</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>0.0003598560575770016 +/- 0.0011921672543683032</t>
+          <t>-0.005877648940423874 +/- 0.001559376249500192</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>-0.0005997600959615657 +/- 0.0011484531480483685</t>
+          <t>0.0013194722111154911 +/- 0.001408549776394139</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
         <is>
-          <t>-0.005037984806077522 +/- 0.001640806439718774</t>
+          <t>-0.0034386245501799697 +/- 0.001581265088627361</t>
         </is>
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>-0.0001599360255897686 +/- 0.0002652238936709711</t>
+          <t>3.998400639743105e-05 +/- 0.00011995201919229316</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>-0.000399840063974366 +/- 0.0006194295635677269</t>
+          <t>-0.00043982407037189696 +/- 0.0007680676814193536</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>0.0006397441023590744 +/- 0.0006496632070880599</t>
+          <t>-0.0011195521791283803 +/- 0.0005597760895641902</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3046,52 +3046,52 @@
       </c>
       <c r="CB6" t="inlineStr">
         <is>
-          <t>0.0025589764094362754 +/- 0.0005423694508696546</t>
+          <t>-0.00019992003198721076 +/- 0.00019992003198721076</t>
         </is>
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>0.0011595361855258224 +/- 0.0010646562939380026</t>
+          <t>-0.0031987205117953387 +/- 0.0017151227980429645</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-3.998400639744215e-05 +/- 0.00011995201919232645</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>0.0008396641343462851 +/- 0.0006797281087565166</t>
+          <t>-0.0014394242303079174 +/- 0.0005984258115592239</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>-0.0025589764094361865 +/- 0.0010303157718293075</t>
+          <t>-0.003518592562974854 +/- 0.001525692445288994</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>-0.007477009196321449 +/- 0.0008006791041383803</t>
+          <t>-0.0014794082367053708 +/- 0.0011732427629845108</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
         <is>
-          <t>3.9984006397453255e-05 +/- 0.0005496892077116146</t>
+          <t>-0.00043982407037188585 +/- 0.0006557864640886235</t>
         </is>
       </c>
       <c r="CI6" t="inlineStr">
         <is>
-          <t>-0.002439024390243871 +/- 0.0013315334510473353</t>
+          <t>-0.00027988804478211725 +/- 0.0005944049878975651</t>
         </is>
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>0.0031587365053978634 +/- 0.001573664026721663</t>
+          <t>0.0014794082367052708 +/- 0.0015898356938881327</t>
         </is>
       </c>
       <c r="CK6" t="inlineStr">
         <is>
-          <t>-0.00043982407037183033 +/- 0.0008281613425512807</t>
+          <t>-0.0011995201919232645 +/- 0.0008575613990215042</t>
         </is>
       </c>
     </row>
@@ -3101,7 +3101,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>0.0034535686876438487 +/- 0.0011511895625479606</t>
+          <t>0.0014198004604758286 +/- 0.0012499230602380919</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -3111,157 +3111,157 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.010437452033768158 +/- 0.001977605330272473</t>
+          <t>0.005794320798158103 +/- 0.001144132886866894</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.007712970069071334 +/- 0.002240469773905613</t>
+          <t>-0.00019186492709133418 +/- 0.000974552962333133</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.000575594781273936 +/- 0.0011543828823093825</t>
+          <t>0.0031082118188795137 +/- 0.0018116763828262186</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>0.004067536454336096 +/- 0.0019506162743113948</t>
+          <t>-0.00034535686876437934 +/- 0.0013342546930709034</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>0.012317728319263189 +/- 0.0027049552645551944</t>
+          <t>0.009746738296239432 +/- 0.0013314928298463122</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.0001151189562547561 +/- 0.00024570699299431313</t>
+          <t>0.00019186492709133418 +/- 0.00046207193318467774</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.010245587106676867 +/- 0.0014052059419493884</t>
+          <t>0.005295471987720635 +/- 0.0016884113584036968</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>0.007559478127398278 +/- 0.004050304511566018</t>
+          <t>0.00406753645433614 +/- 0.0028674661077926944</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
         <is>
-          <t>0.007866462010744379 +/- 0.0045379198812448545</t>
+          <t>-0.0016884113584036743 +/- 0.005542738322415274</t>
         </is>
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>-7.674597083657808e-05 +/- 0.001402583797582276</t>
+          <t>0.002916346891788191 +/- 0.0014782317946475884</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>0.005103607060629267 +/- 0.0010303700369990794</t>
+          <t>0.002993092862624713 +/- 0.00169711008346094</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>0.009286262471220197 +/- 0.002029056648718692</t>
+          <t>0.005947812739831149 +/- 0.0021174796103332915</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>0.005487336914811902 +/- 0.0046873194636032015</t>
+          <t>0.00349194167306216 +/- 0.001982439194641512</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>0.013123561013046781 +/- 0.0020363007154906554</t>
+          <t>0.0010744435917114492 +/- 0.0023202174148627746</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>0.00982348426707592 +/- 0.0015463884635157047</t>
+          <t>0.0011511895625479717 +/- 0.001163910275372455</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>0.0009593246354565932 +/- 0.0018342929244385617</t>
+          <t>0.0007674597083653145 +/- 0.0007480271945363659</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>-0.008672294704528072 +/- 0.0016207760615458858</t>
+          <t>-0.00698388334612432 +/- 0.002209697628378829</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>-0.0017651573292402634 +/- 0.0011664377708035935</t>
+          <t>0.0040675364543361296 +/- 0.0013534299377243619</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>-0.0004221028396009463 +/- 0.0004988488104374424</t>
+          <t>-0.00046047582501920206 +/- 0.0004475020640710282</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-0.0013430544896393393 +/- 0.0024284370425628147</t>
+          <t>-0.0035686876438986827 +/- 0.0018958740333132086</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.002340752110514155 +/- 0.0013119970066982922</t>
+          <t>0.0013814274750575505 +/- 0.0013750171041572428</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>3.837298541821132e-05 +/- 0.0009925185845262743</t>
+          <t>0.003300076745970848 +/- 0.0011664377708035711</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>0.0013430544896392393 +/- 0.0009895469653283047</t>
+          <t>0.005909439754412893 +/- 0.001178993975114135</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.000537221795855769 +/- 0.001458173445894101</t>
+          <t>-0.00011511895625480051 +/- 0.001125970894176605</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>-0.0017267843438220076 +/- 0.0008958263645379237</t>
+          <t>0.0004221028396009352 +/- 0.0004358333342901355</t>
         </is>
       </c>
       <c r="AC7" t="inlineStr">
         <is>
-          <t>-0.006216423637759083 +/- 0.0013490710538178808</t>
+          <t>0.0026861089792785896 +/- 0.00232782055074493</t>
         </is>
       </c>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>-0.0034535686876439485 +/- 0.0011764934548546275</t>
+          <t>-0.0007290867229470255 +/- 0.001480719983236747</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>0.00038372985418261285 +/- 0.0009080705730006923</t>
+          <t>-0.0009593246354566376 +/- 0.0012522769663914628</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.002954719877206402 +/- 0.0010723859257468981</t>
+          <t>-0.0019186492709132863 +/- 0.001261064982744053</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.837298541821132e-05 +/- 0.0007168665269481532</t>
+          <t>0.0008442056792018593 +/- 0.0006601938040708121</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.0006523407521105473 +/- 0.0006432484502778324</t>
+          <t>0.000690713737528803 +/- 0.0006601938040708302</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
@@ -3271,122 +3271,122 @@
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.00414428242517263 +/- 0.0014940845996877902</t>
+          <t>0.00046047582501917983 +/- 0.0010961517158162468</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>0.0008442056792018037 +/- 0.0010826351480940758</t>
+          <t>0.001995395241749809 +/- 0.0011864639166339357</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>-0.0003069838833461458 +/- 0.0003759769367280319</t>
+          <t>0.0006139677666922693 +/- 0.00035169422064128893</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>0.0003069838833460681 +/- 0.0005639654050920316</t>
+          <t>0.0010360706062931824 +/- 0.0008758796784737754</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>0.001650038372985363 +/- 0.0011389732985154512</t>
+          <t>-0.0024174980813507106 +/- 0.000971526393029339</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>0.004796623177283144 +/- 0.0014073001397461409</t>
+          <t>-0.0007290867229470588 +/- 0.001334254693070888</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-0.000767459708365359 +/- 0.0008750386992318743</t>
+          <t>-0.00023023791250960103 +/- 0.0005480758579081421</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-0.0006523407521105473 +/- 0.0006199345518573829</t>
+          <t>0.0014198004604758507 +/- 0.0008058326937835687</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-0.0010360706062932379 +/- 0.0013408599546934948</t>
+          <t>-0.0023407521105142104 +/- 0.0015392303238780795</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
         <is>
-          <t>0.004182655410590897 +/- 0.0011945036390079327</t>
+          <t>-0.00026861089792787893 +/- 0.0009249401990171922</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-0.0008442056792018926 +/- 0.0009976976208749104</t>
+          <t>-0.0019570222563315308 +/- 0.0009623895782029379</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>0.006600153491941629 +/- 0.0013381117248014347</t>
+          <t>0.004528012279355342 +/- 0.0010689476805206479</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>0.0007290867229469922 +/- 0.0007371209789830462</t>
+          <t>0.003530314658480438 +/- 0.0008194227361497829</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>0.0005755947812739581 +/- 0.0011796182769715506</t>
+          <t>0.00176515732924023 +/- 0.0012279355333844949</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>-0.0005755947812740025 +/- 0.00030937289901376906</t>
+          <t>0.0007290867229470699 +/- 0.00046840198064981256</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>3.837298541821132e-05 +/- 0.0010914399580451025</t>
+          <t>0.004412893323100542 +/- 0.0010043171395473808</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>0.0038756715272447507 +/- 0.0011441328868668904</t>
+          <t>0.007137375287797398 +/- 0.0013750171041572417</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-0.00034535686876443485 +/- 0.0011311897907124863</t>
+          <t>0.0010360706062931713 +/- 0.000986566395409247</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>0.003108211818879458 +/- 0.002298858910322356</t>
+          <t>0.0011511895625479717 +/- 0.00158215872049794</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-3.3306690738754695e-17 +/- 0.000297235866938372</t>
+          <t>0.00030698388334613467 +/- 0.0005090751788726802</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>0.00034535686876432383 +/- 0.0004358333342900896</t>
+          <t>0.000690713737528803 +/- 0.0002871571286856537</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
-          <t>0.00019186492709128978 +/- 0.0002574138116845089</t>
+          <t>0.0004221028396009352 +/- 0.00031874995636678265</t>
         </is>
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>0.006638526477359874 +/- 0.001044563130377284</t>
+          <t>0.0004988488104374688 +/- 0.0012380864009901558</t>
         </is>
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>0.0026861089792785454 +/- 0.0008230088484085622</t>
+          <t>0.007290867229470454 +/- 0.00204495972286635</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3396,92 +3396,92 @@
       </c>
       <c r="BI7" t="inlineStr">
         <is>
-          <t>-0.00026861089792790116 +/- 0.0005704554392677598</t>
+          <t>0.00030698388334613467 +/- 0.00033452793120037</t>
         </is>
       </c>
       <c r="BJ7" t="inlineStr">
         <is>
-          <t>-0.00038372985418270165 +/- 0.0015634342891376262</t>
+          <t>0.0037989255564082835 +/- 0.0014505800592046086</t>
         </is>
       </c>
       <c r="BK7" t="inlineStr">
         <is>
-          <t>-0.0015732924021489402 +/- 0.0006523407521105362</t>
+          <t>-0.0033768227168073706 +/- 0.0009368039612996251</t>
         </is>
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>-0.00034535686876442374 +/- 0.0007760456030758457</t>
+          <t>0.00019186492709133418 +/- 0.00042902301947426427</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>-0.0016884113584037298 +/- 0.0014378353027778318</t>
+          <t>-0.000882578664620115 +/- 0.0010159786872504812</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>-0.0031465848042978362 +/- 0.0010826351480940782</t>
+          <t>-0.0021105141980046205 +/- 0.0016836079024159993</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>0.005640828856484992 +/- 0.001273266310286796</t>
+          <t>-3.8372985418266833e-05 +/- 0.0012893551509141625</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>0.004758250191864888 +/- 0.0013856845806038314</t>
+          <t>0.0007290867229470477 +/- 0.0015487671581435743</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>-0.0004221028396009352 +/- 0.00011511895625480051</t>
+          <t>3.8372985418266833e-05 +/- 0.00020664485061913608</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>0.0027628549501150677 +/- 0.0010123488839810322</t>
+          <t>-0.002455871066768989 +/- 0.0011409108785355778</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.00038372985418260174 +/- 0.0013069367894034127</t>
+          <t>-0.0020721412125863314 +/- 0.0004604758250191632</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.0008058326937835147 +/- 0.0008991077907797291</t>
+          <t>0.0004221028396009241 +/- 0.0009312863468543143</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>0.0034919416730621266 +/- 0.002011930426541552</t>
+          <t>0.0026861089792785896 +/- 0.0008407099884960269</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>0.0028779739063698575 +/- 0.0011920356536461233</t>
+          <t>0.005257099002302368 +/- 0.0007290867229470343</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
         <is>
-          <t>0.0008825786646200484 +/- 0.0013946877855246385</t>
+          <t>0.0007290867229470588 +/- 0.0012428345925327372</t>
         </is>
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>-0.0004988488104374688 +/- 0.00024570699299436165</t>
+          <t>7.674597083653367e-05 +/- 0.00015349194167306733</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>-0.0009593246354566709 +/- 0.0006006322272639699</t>
+          <t>-0.001304681504221039 +/- 0.0005480758579081047</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>-0.000729086722947092 +/- 0.0007760456030758402</t>
+          <t>-0.00030698388334613467 +/- 0.0005639654050920785</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="CB7" t="inlineStr">
         <is>
-          <t>0.0013430544896392282 +/- 0.0006478105531901267</t>
+          <t>0.0016884113584037074 +/- 0.000548075857908097</t>
         </is>
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>0.0033768227168073373 +/- 0.0008012514588572813</t>
+          <t>-0.0015349194167306513 +/- 0.000454035286500332</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
@@ -3506,37 +3506,37 @@
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>0.0015349194167305735 +/- 0.0008580460389485036</t>
+          <t>0.00030698388334613467 +/- 0.0005894969875570888</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>0.0013430544896392393 +/- 0.0013967977531236602</t>
+          <t>-0.000690713737528803 +/- 0.0006374999127335653</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>0.0004988488104374245 +/- 0.0015544611742539661</t>
+          <t>0.0019186492709132863 +/- 0.0006187457980274899</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
         <is>
-          <t>-0.0009976976208749377 +/- 0.000623487214477071</t>
+          <t>0.0009593246354566709 +/- 0.00042902301947426427</t>
         </is>
       </c>
       <c r="CI7" t="inlineStr">
         <is>
-          <t>-0.00011511895625484491 +/- 0.0016011240249443484</t>
+          <t>-0.003108211818879503 +/- 0.0005547518148427263</t>
         </is>
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>-0.0004988488104375021 +/- 0.001466731761597563</t>
+          <t>-0.0034535686876439042 +/- 0.001201264454527908</t>
         </is>
       </c>
       <c r="CK7" t="inlineStr">
         <is>
-          <t>-0.00038372985418271276 +/- 0.0012374915960550279</t>
+          <t>0.0055257099002302135 +/- 0.0006466730447564418</t>
         </is>
       </c>
     </row>
@@ -3546,7 +3546,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>-0.006493506493506518 +/- 0.0020287054902058065</t>
+          <t>-0.00427314620863013 +/- 0.0022231251213106866</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -3556,157 +3556,157 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>0.004775869291998303 +/- 0.0029277595659247704</t>
+          <t>-0.0015919564306661749 +/- 0.002462830072341704</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>0.0007540846250523314 +/- 0.0017354264915968164</t>
+          <t>0.011646418098030954 +/- 0.0019809954616735433</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>-0.004021784666945982 +/- 0.002113032293744173</t>
+          <t>-0.003812316715542552 +/- 0.0016056780810001412</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>0.00029325513196477583 +/- 0.0018072605454648785</t>
+          <t>0.009090909090909049 +/- 0.0020095827323354113</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>0.006577293674067864 +/- 0.001717637201508169</t>
+          <t>0.012651864264767443 +/- 0.001620366954823105</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.0002932551319648535 +/- 0.0002682498633193765</t>
+          <t>0.00041893590280682734 +/- 0.0007256182687762324</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-0.0004608294930876111 +/- 0.0017114954516812178</t>
+          <t>-0.0012987012987013436 +/- 0.0026591706866457335</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>0.028361960620025096 +/- 0.00319629150569124</t>
+          <t>0.02945119396732294 +/- 0.0022796427080708287</t>
         </is>
       </c>
       <c r="L8" t="inlineStr">
         <is>
-          <t>0.016673648931713424 +/- 0.002996490111813598</t>
+          <t>0.045957268537913654 +/- 0.003803098187444108</t>
         </is>
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>0.00226225387515705 +/- 0.0018660291119665005</t>
+          <t>8.378718056131217e-05 +/- 0.0013087975996492296</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>-0.0012149141181399647 +/- 0.001176755082127202</t>
+          <t>0.0016757436112274204 +/- 0.002859832118286724</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>0.006493506493506473 +/- 0.0012033017692790083</t>
+          <t>0.0023460410557184174 +/- 0.001984536117691999</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>0.009049015500628366 +/- 0.0036435383167421763</t>
+          <t>0.014620863007959718 +/- 0.002571938915487375</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
         <is>
-          <t>0.01068286552157518 +/- 0.003450821593667539</t>
+          <t>0.013573523250942543 +/- 0.004305878561384023</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>-0.0012987012987013213 +/- 0.0019420740656052374</t>
+          <t>0.008169250104733928 +/- 0.0019492903433819555</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>-0.0020527859237536973 +/- 0.0008047495899580283</t>
+          <t>0.0003770423125261213 +/- 0.0017818324522946847</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
         <is>
-          <t>-0.0015081692501047628 +/- 0.0019124779573545755</t>
+          <t>0.0037285295349811067 +/- 0.0020304349922166177</t>
         </is>
       </c>
       <c r="U8" t="inlineStr">
         <is>
-          <t>-0.004985337243401777 +/- 0.0017419876737571557</t>
+          <t>0.0030163385002094146 +/- 0.0011819636346598894</t>
         </is>
       </c>
       <c r="V8" t="inlineStr">
         <is>
-          <t>0.00016757436112272429 +/- 0.0005364997266387114</t>
+          <t>0.00016757436112269097 +/- 0.0005682723069229405</t>
         </is>
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>0.007247591118558827 +/- 0.002443154304453012</t>
+          <t>0.011562630917469563 +/- 0.0024939884484519795</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>-0.006409719312945128 +/- 0.001377401107898923</t>
+          <t>-0.0015919564306661528 +/- 0.002142725069550811</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>0.002262253875157061 +/- 0.0016778369832007244</t>
+          <t>0.0009216589861750779 +/- 0.0008747638465781553</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>-0.004524507750314233 +/- 0.0010565161468721</t>
+          <t>0.0005865102639295849 +/- 0.0011730205278592373</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-0.001801424382069583 +/- 0.0013900846269825683</t>
+          <t>0.004943443653121016 +/- 0.0019088036447246534</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>-0.0007540846250523869 +/- 0.0009140102316410249</t>
+          <t>-0.0002513615416841697 +/- 0.0005364997266387027</t>
         </is>
       </c>
       <c r="AC8" t="inlineStr">
         <is>
-          <t>0.011436950146627522 +/- 0.0027665633818347735</t>
+          <t>0.016883116883116833 +/- 0.0022564278189351047</t>
         </is>
       </c>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>-0.009384164222873914 +/- 0.005639941609567307</t>
+          <t>-0.008797653958944319 +/- 0.0035000584120997978</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>-0.002764976958525378 +/- 0.0028794034817661743</t>
+          <t>-0.0030163385002094922 +/- 0.001735426491596811</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>-0.005906996229576888 +/- 0.0026392961876832775</t>
+          <t>-0.0016338500209468366 +/- 0.00297680417653802</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0004608294930875112 +/- 0.0004758197189610557</t>
+          <t>0.001173020527859181 +/- 0.0010227528794079183</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.000795978215333093 +/- 0.0009264073895054861</t>
+          <t>-4.4408920985006264e-17 +/- 0.0005620614941348428</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
@@ -3716,122 +3716,122 @@
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>-0.0055299539170507225 +/- 0.0021671583001889516</t>
+          <t>-0.006744868035190654 +/- 0.0016273920904528562</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>-0.004733975701717663 +/- 0.002853996033556954</t>
+          <t>0.00548806032676995 +/- 0.002236113304580219</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>0.000921658986175089 +/- 0.0010397715664843634</t>
+          <t>-0.0005865102639296737 +/- 0.00033514872224549015</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>-0.0007121910347717142 +/- 0.0008595846053072041</t>
+          <t>0.0028068705488059954 +/- 0.0011249033583659446</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>-0.0023460410557185063 +/- 0.001975672580234877</t>
+          <t>0.005823209049015443 +/- 0.001616571544329679</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>-0.007708420611646438 +/- 0.0023415481545843715</t>
+          <t>-0.004398826979472192 +/- 0.0020883860210497763</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-0.0018852115626309506 +/- 0.001379947137997529</t>
+          <t>0.001968998743192241 +/- 0.0009377054581315215</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.0034352744030162973 +/- 0.0013995218339748585</t>
+          <t>-0.0012568077084206598 +/- 0.0014390920852381658</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-0.005488060326770028 +/- 0.001572544983588055</t>
+          <t>0.0006702974444909304 +/- 0.002296135669215703</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
         <is>
-          <t>-0.00041893590280689397 +/- 0.0016116785975426409</t>
+          <t>0.003183912861332161 +/- 0.0010956595584936718</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-0.020276497695852568 +/- 0.0011878883015297738</t>
+          <t>-0.004608294930875623 +/- 0.0014752255434988546</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>-0.02199413489736073 +/- 0.0011280194401203404</t>
+          <t>-0.013196480938416489 +/- 0.002162699539026441</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>0.004524507750314178 +/- 0.0015875404542519</t>
+          <t>0.0082111436950146 +/- 0.0022653549785665306</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>0.0024298282362798075 +/- 0.0012540116922577086</t>
+          <t>0.003393380812735591 +/- 0.0022980457732555476</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>-0.0012987012987013325 +/- 0.0009635525764558048</t>
+          <t>0.0008797653958943829 +/- 0.0009993180093738235</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>0.004733975701717597 +/- 0.0017480222911625608</t>
+          <t>0.005571847507331329 +/- 0.0010439828901866073</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>-0.00310012568077086 +/- 0.0017191692106144252</t>
+          <t>-0.0011311269375786082 +/- 0.002355373740573208</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-0.007247591118558883 +/- 0.0012851161835088303</t>
+          <t>-0.008336824465856773 +/- 0.0017916551973475659</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-0.016087138667783864 +/- 0.0019667690983335537</t>
+          <t>-0.0008797653958944829 +/- 0.0023952731225677067</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-0.0012987012987013325 +/- 0.0009815981997368921</t>
+          <t>-0.0015919564306661528 +/- 0.000969906736723095</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>0.0006284038542102577 +/- 0.0010132707685335286</t>
+          <t>-0.004231252618349446 +/- 0.0007364221127460074</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
-          <t>-0.0036866359447004894 +/- 0.0005865102639296103</t>
+          <t>-0.005194805194805241 +/- 0.0011427047923741592</t>
         </is>
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>-0.008043569333891942 +/- 0.0021752417236275117</t>
+          <t>-0.005446166736489367 +/- 0.0023772536169436426</t>
         </is>
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>-0.006200251361541708 +/- 0.001954236077032357</t>
+          <t>0.011981566820276467 +/- 0.001547229603068234</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3841,92 +3841,92 @@
       </c>
       <c r="BI8" t="inlineStr">
         <is>
-          <t>-0.0026392961876833152 +/- 0.0006227929931847129</t>
+          <t>-0.005739421868454164 +/- 0.0011403986249531736</t>
         </is>
       </c>
       <c r="BJ8" t="inlineStr">
         <is>
-          <t>-0.0025555090071219476 +/- 0.0019510902425127904</t>
+          <t>0.0150397989107666 +/- 0.001480569505410339</t>
         </is>
       </c>
       <c r="BK8" t="inlineStr">
         <is>
-          <t>-0.01834939254294097 +/- 0.002042070818090318</t>
+          <t>0.0022203602848763658 +/- 0.0016551944922612789</t>
         </is>
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>-0.00012568077084209594 +/- 0.001243470639267352</t>
+          <t>-0.0004189359028069162 +/- 0.0010261791968090247</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>-0.0010473397570172182 +/- 0.0017699732027044732</t>
+          <t>0.011562630917469586 +/- 0.00165678424242022</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>-0.016506074570590744 +/- 0.002341548154584341</t>
+          <t>0.003309593632174235 +/- 0.0016273920904528616</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>-0.007163803937997504 +/- 0.0016594304415867961</t>
+          <t>-0.0027230833682447054 +/- 0.0024517595120904147</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>-0.0010473397570172072 +/- 0.0012602940055711053</t>
+          <t>0.00356095517385836 +/- 0.0019129367502020668</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>4.1893590280661644e-05 +/- 0.0002932551319648218</t>
+          <t>0.00041893590280683846 +/- 0.0004189359028068385</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>-0.007415165479681629 +/- 0.002018297355751296</t>
+          <t>0.00020946795140337483 +/- 0.001173768389285448</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>-0.00418935902806874 +/- 0.001845221243866382</t>
+          <t>-0.0038123167155425853 +/- 0.0019330158349492015</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>-0.0004189359028069051 +/- 0.0005924648355144948</t>
+          <t>0.0005865102639295739 +/- 0.0012314150361708593</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>0.007331378299120217 +/- 0.0012321274545331105</t>
+          <t>0.005865102639296127 +/- 0.0033514872224549696</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>-0.007666527021365765 +/- 0.0022719307688238476</t>
+          <t>-0.0005865102639296627 +/- 0.002062594658582512</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
         <is>
-          <t>-0.00582320904901551 +/- 0.0021067936255852846</t>
+          <t>-0.005613741097612113 +/- 0.001866029111966506</t>
         </is>
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>-0.0010054461667365123 +/- 0.0005027230833682284</t>
+          <t>-0.0005446166736489677 +/- 0.0004210253716431147</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>-0.00108923334729788 +/- 0.0011878883015297534</t>
+          <t>-0.0017176372015082042 +/- 0.0013438638401629848</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>-0.0006284038542103354 +/- 0.0008636584888180851</t>
+          <t>-0.0024717218265605913 +/- 0.0013568608915543795</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3936,52 +3936,52 @@
       </c>
       <c r="CB8" t="inlineStr">
         <is>
-          <t>0.0010054461667364678 +/- 0.0005983601532084507</t>
+          <t>0.002136573104314998 +/- 0.0009451624778113523</t>
         </is>
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>-0.008420611646418108 +/- 0.001690861840855509</t>
+          <t>-0.002890657729367452 +/- 0.001304095719838572</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>0.00012568077084205154 +/- 0.0001919805485947</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>-0.0010054461667365234 +/- 0.0007770103473394034</t>
+          <t>0.0002932551319647536 +/- 0.0009562389786772696</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>-0.006996229576874758 +/- 0.002450327409449472</t>
+          <t>-0.004147465437788078 +/- 0.002131638748757186</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>0.00041893590280684957 +/- 0.0018067749185461056</t>
+          <t>0.009174696271470417 +/- 0.0019330158349492208</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
         <is>
-          <t>-0.0007121910347717031 +/- 0.0008595846053072078</t>
+          <t>0.0011311269375785082 +/- 0.0011249033583659257</t>
         </is>
       </c>
       <c r="CI8" t="inlineStr">
         <is>
-          <t>-0.001717637201508193 +/- 0.0017818324522946504</t>
+          <t>0.0012568077084205709 +/- 0.0023992997173483705</t>
         </is>
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>0.003560955173858371 +/- 0.0020025837289848547</t>
+          <t>-0.002052785923753708 +/- 0.002762754435491834</t>
         </is>
       </c>
       <c r="CK8" t="inlineStr">
         <is>
-          <t>-0.004733975701717663 +/- 0.001200381129609912</t>
+          <t>-0.0036866359447005116 +/- 0.0017950804596253316</t>
         </is>
       </c>
     </row>
@@ -3991,7 +3991,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>-0.003037869330004128 +/- 0.0011777754222293039</t>
+          <t>0.0005826050769870972 +/- 0.0016873187626061895</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4001,157 +4001,157 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>-0.016063254265501405 +/- 0.0013827089243309287</t>
+          <t>-0.006991260923845199 +/- 0.0013000831753485723</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>-0.0028297960882230242 +/- 0.0013133361496512274</t>
+          <t>0.0032459425717852653 +/- 0.0010494814992025264</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>-0.0020807324178110376 +/- 0.0016645859342488522</t>
+          <t>-0.0014981273408239738 +/- 0.0011350962710766409</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>-0.0028714107365792273 +/- 0.0009388692611467663</t>
+          <t>0.00024968789013732893 +/- 0.0013446104387352137</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-0.018019142738243843 +/- 0.0020811485226883237</t>
+          <t>-0.013566375364128158 +/- 0.0017478152309613121</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.0003223456800838474</t>
+          <t>-4.161464835622519e-05 +/- 0.00034567723108276465</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.008739076154806524 +/- 0.001147236683486498</t>
+          <t>0.008322929671244284 +/- 0.0017557239375554552</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>0.002163961714523532 +/- 0.0031681841549187325</t>
+          <t>-0.0014148980441115345 +/- 0.00258681153024055</t>
         </is>
       </c>
       <c r="L9" t="inlineStr">
         <is>
-          <t>0.0062005826050769985 +/- 0.00211744556524486</t>
+          <t>0.005784436121514769 +/- 0.0025206937529600806</t>
         </is>
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>-0.0038285476487723404 +/- 0.0011135320982321986</t>
+          <t>-0.003662089055347484 +/- 0.0016832083575660996</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>-0.011735330836454384 +/- 0.002481573286038379</t>
+          <t>-0.0013316687473990951 +/- 0.0011887521312597335</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>-0.006200582605076966 +/- 0.0010763643076469205</t>
+          <t>-0.007781939242613412 +/- 0.0015797130999668813</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>0.006491885143570552 +/- 0.002943776809625871</t>
+          <t>-0.0013732833957553093 +/- 0.005492660668932857</t>
         </is>
       </c>
       <c r="Q9" t="inlineStr">
         <is>
-          <t>-0.017935913441531382 +/- 0.00398914988980536</t>
+          <t>-0.012193091968372871 +/- 0.004752276232378085</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>0.001955888472742451 +/- 0.0009679320307626112</t>
+          <t>0.0006242197253433224 +/- 0.0025602311136532782</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>-0.0009571369121930573 +/- 0.001177775422229284</t>
+          <t>0.004411152725759482 +/- 0.0015142243361348504</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
         <is>
-          <t>-0.0003329171868497238 +/- 0.001439169077469057</t>
+          <t>-0.0025384935497295147 +/- 0.002042512058561466</t>
         </is>
       </c>
       <c r="U9" t="inlineStr">
         <is>
-          <t>0.004078235538909736 +/- 0.0014270851601732887</t>
+          <t>-0.000540990428630872 +/- 0.0017855545528859848</t>
         </is>
       </c>
       <c r="V9" t="inlineStr">
         <is>
-          <t>-4.1614648356202987e-05 +/- 0.00022410173978918454</t>
+          <t>2.2204460492503132e-17 +/- 0.00045586563254695585</t>
         </is>
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>0.004494382022471932 +/- 0.0021446689515979976</t>
+          <t>0.004452767374115696 +/- 0.0015125078523001527</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>-0.0003329171868497349 +/- 0.0013523160057654564</t>
+          <t>0.00037453183520598233 +/- 0.000901223796408975</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>-4.161464835618078e-05 +/- 0.001026963185955308</t>
+          <t>0.00033291718684975714 +/- 0.0010658550540878634</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>-4.161464835618078e-05 +/- 0.001183642334858763</t>
+          <t>-0.001581356637536413 +/- 0.000888645713860284</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.001955888472742384 +/- 0.0009126804910304234</t>
+          <t>-0.001622971285892638 +/- 0.0005409904286308822</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>0.00029130253849357635 +/- 0.0004182220399967019</t>
+          <t>-0.00029130253849356523 +/- 0.00032502079383715874</t>
         </is>
       </c>
       <c r="AC9" t="inlineStr">
         <is>
-          <t>0.0032459425717853096 +/- 0.000828121046280993</t>
+          <t>0.0019142738243861923 +/- 0.0016770238601423334</t>
         </is>
       </c>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>-0.002205576362879702 +/- 0.0011923885794335805</t>
+          <t>0.0023304203079484 +/- 0.0010560613849729082</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>0.0024968789013733116 +/- 0.0009305318258425998</t>
+          <t>0.0027049521431543933 +/- 0.0008778619687777368</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.005617977528089913 +/- 0.001279269758546764</t>
+          <t>0.004744069912609239 +/- 0.0012785927170817634</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>-0.00016645859342484526 +/- 0.0004993757802746561</t>
+          <t>-0.0004161464835622075 +/- 0.0004161464835622075</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.00033291718684974603 +/- 0.0005826050769870814</t>
+          <t>-0.0006658343736995476 +/- 0.000499375780274656</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
@@ -4161,272 +4161,272 @@
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>-0.0023720349563045697 +/- 0.0009498720108625209</t>
+          <t>0.005409904286308798 +/- 0.0012484394506866595</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>-0.0009987515605492825 +/- 0.00168731876260618</t>
+          <t>0.0035372451102788304 +/- 0.00100652406345801</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>-4.161464835619189e-05 +/- 0.0004726515477153758</t>
+          <t>-0.0003745318352060156 +/- 0.00034567723108273657</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>0.0007906783187682342 +/- 0.000601615992293013</t>
+          <t>-0.00029130253849356523 +/- 0.0005280306924864484</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>-0.002247191011235927 +/- 0.0007939568884036336</t>
+          <t>0.0017894298793175278 +/- 0.0016960202973212513</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>-0.0034540158135663466 +/- 0.0007684638082654759</t>
+          <t>0.0027881814398668324 +/- 0.0017952271835308532</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-0.00020807324178108156 +/- 0.0006774373947606972</t>
+          <t>4.161464835621409e-05 +/- 0.000601615992293009</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-0.0006658343736995031 +/- 0.0012649757930562279</t>
+          <t>-0.0006242197253433224 +/- 0.001480101476802222</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>0.00024968789013736227 +/- 0.0011041613950413213</t>
+          <t>0.0012484394506866337 +/- 0.0012758809585314867</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
         <is>
-          <t>0.002829796088223091 +/- 0.0010978698259070086</t>
+          <t>0.006408655846858102 +/- 0.0011041613950413271</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-0.0022471910112359162 +/- 0.0008964069591568237</t>
+          <t>-0.0024968789013732782 +/- 0.00147717347892625</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>-0.005243445692883875 +/- 0.0008964069591567886</t>
+          <t>-0.0066167290886392175 +/- 0.0013982769551736543</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>4.16146483562585e-05 +/- 0.0011235955056179846</t>
+          <t>-0.0008739076154806625 +/- 0.0019291430689137327</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>-0.0021223470661672628 +/- 0.0016378417523224857</t>
+          <t>-0.0028297960882230576 +/- 0.001188752131259735</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>-0.00012484394506862007 +/- 0.0005598678338357575</t>
+          <t>-0.0007074490220557617 +/- 0.0006460330710053999</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>-0.0025384935497294813 +/- 0.001009959309156199</t>
+          <t>0.002413649604660839 +/- 0.0014511523740460054</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>0.00033291718684980154 +/- 0.001174093714495717</t>
+          <t>-0.0014981273408239848 +/- 0.0016031094701838017</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>0.0013316687473991396 +/- 0.0010494814992025334</t>
+          <t>-0.004494382022471921 +/- 0.0014981273408239861</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-0.0036620890553474617 +/- 0.0011592499606478558</t>
+          <t>-0.0018726591760299671 +/- 0.0012792697585467623</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>0.00033291718684980154 +/- 0.000739758170396623</t>
+          <t>-0.000499375780274669 +/- 0.0008487756160787092</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>-0.0005826050769870639 +/- 0.000934246538520342</t>
+          <t>-0.0015397419891801877 +/- 0.0006975886231477587</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
-          <t>0.00029130253849357635 +/- 0.0002664637635219906</t>
+          <t>-4.161464835622519e-05 +/- 0.00022410173978922162</t>
         </is>
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>-0.003745318352059901 +/- 0.002517600243404788</t>
+          <t>-0.0004161464835621964 +/- 0.001429510115465472</t>
         </is>
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>0.002621722846441987 +/- 0.001355513730745092</t>
+          <t>-0.001081980857261766 +/- 0.0011041613950413271</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
         <is>
+          <t>4.161464835622519e-05 +/- 0.00012484394506867558</t>
+        </is>
+      </c>
+      <c r="BI9" t="inlineStr">
+        <is>
+          <t>-0.000499375780274669 +/- 0.000552080697520671</t>
+        </is>
+      </c>
+      <c r="BJ9" t="inlineStr">
+        <is>
+          <t>-0.0006658343736995476 +/- 0.0013446104387352096</t>
+        </is>
+      </c>
+      <c r="BK9" t="inlineStr">
+        <is>
+          <t>0.000540990428630883 +/- 0.001756217049189301</t>
+        </is>
+      </c>
+      <c r="BL9" t="inlineStr">
+        <is>
+          <t>-0.0009987515605493047 +/- 0.000856898055845766</t>
+        </is>
+      </c>
+      <c r="BM9" t="inlineStr">
+        <is>
+          <t>-0.001081980857261766 +/- 0.0011041613950413271</t>
+        </is>
+      </c>
+      <c r="BN9" t="inlineStr">
+        <is>
+          <t>-0.00041614648356221864 +/- 0.001019346542980943</t>
+        </is>
+      </c>
+      <c r="BO9" t="inlineStr">
+        <is>
+          <t>-0.0030794839783603867 +/- 0.0019975031210986384</t>
+        </is>
+      </c>
+      <c r="BP9" t="inlineStr">
+        <is>
+          <t>0.0022888056595921857 +/- 0.0013192565529877274</t>
+        </is>
+      </c>
+      <c r="BQ9" t="inlineStr">
+        <is>
+          <t>-8.322929671243929e-05 +/- 0.0003627880935115103</t>
+        </is>
+      </c>
+      <c r="BR9" t="inlineStr">
+        <is>
+          <t>0.0009155222638368765 +/- 0.0019412241014882467</t>
+        </is>
+      </c>
+      <c r="BS9" t="inlineStr">
+        <is>
+          <t>0.0022055763628797465 +/- 0.000790678318768215</t>
+        </is>
+      </c>
+      <c r="BT9" t="inlineStr">
+        <is>
+          <t>0.0005409904286308942 +/- 0.00045776113191843575</t>
+        </is>
+      </c>
+      <c r="BU9" t="inlineStr">
+        <is>
+          <t>0.003245942571785276 +/- 0.0017238714254854924</t>
+        </is>
+      </c>
+      <c r="BV9" t="inlineStr">
+        <is>
+          <t>0.00578443612151478 +/- 0.0009012237964089634</t>
+        </is>
+      </c>
+      <c r="BW9" t="inlineStr">
+        <is>
+          <t>0.00012484394506867558 +/- 0.0017952271835308376</t>
+        </is>
+      </c>
+      <c r="BX9" t="inlineStr">
+        <is>
+          <t>-0.00020807324178111485 +/- 0.0003355080211526754</t>
+        </is>
+      </c>
+      <c r="BY9" t="inlineStr">
+        <is>
+          <t>-0.00020807324178110376 +/- 0.0005345498368150425</t>
+        </is>
+      </c>
+      <c r="BZ9" t="inlineStr">
+        <is>
+          <t>0.0005826050769871082 +/- 0.00042438780803934044</t>
+        </is>
+      </c>
+      <c r="CA9" t="inlineStr">
+        <is>
           <t>0.0 +/- 0.0</t>
         </is>
       </c>
-      <c r="BI9" t="inlineStr">
-        <is>
-          <t>-0.0004993757802746135 +/- 0.0008689393681989507</t>
-        </is>
-      </c>
-      <c r="BJ9" t="inlineStr">
-        <is>
-          <t>-0.0016229712858925938 +/- 0.0008817985892807761</t>
-        </is>
-      </c>
-      <c r="BK9" t="inlineStr">
-        <is>
-          <t>-0.0044527673741156515 +/- 0.0011629786610472</t>
-        </is>
-      </c>
-      <c r="BL9" t="inlineStr">
-        <is>
-          <t>0.00037453183520603784 +/- 0.0006566680748256183</t>
-        </is>
-      </c>
-      <c r="BM9" t="inlineStr">
-        <is>
-          <t>0.0013316687473991285 +/- 0.0012175396453040221</t>
-        </is>
-      </c>
-      <c r="BN9" t="inlineStr">
-        <is>
-          <t>-0.0006242197253432779 +/- 0.0013323188176098508</t>
-        </is>
-      </c>
-      <c r="BO9" t="inlineStr">
-        <is>
-          <t>-0.001872659176029945 +/- 0.0016251039691857396</t>
-        </is>
-      </c>
-      <c r="BP9" t="inlineStr">
-        <is>
-          <t>0.0010819808572617995 +/- 0.00067615800288272</t>
-        </is>
-      </c>
-      <c r="BQ9" t="inlineStr">
-        <is>
-          <t>0.00012484394506867558 +/- 0.00019070227611137156</t>
-        </is>
-      </c>
-      <c r="BR9" t="inlineStr">
-        <is>
-          <t>0.0037037037037037424 +/- 0.0013218793320240118</t>
-        </is>
-      </c>
-      <c r="BS9" t="inlineStr">
-        <is>
-          <t>0.00020807324178114816 +/- 0.0009535113805567803</t>
-        </is>
-      </c>
-      <c r="BT9" t="inlineStr">
-        <is>
-          <t>-0.0017894298793174833 +/- 0.0008935043925752824</t>
-        </is>
-      </c>
-      <c r="BU9" t="inlineStr">
-        <is>
-          <t>-4.161464835619189e-05 +/- 0.002305391424796419</t>
-        </is>
-      </c>
-      <c r="BV9" t="inlineStr">
-        <is>
-          <t>-0.0012900540990428144 +/- 0.000957136912193095</t>
-        </is>
-      </c>
-      <c r="BW9" t="inlineStr">
-        <is>
-          <t>0.002621722846441987 +/- 0.0023248402369477235</t>
-        </is>
-      </c>
-      <c r="BX9" t="inlineStr">
-        <is>
-          <t>0.0004161464835622519 +/- 0.0001861063651685388</t>
-        </is>
-      </c>
-      <c r="BY9" t="inlineStr">
-        <is>
-          <t>0.0006242197253433668 +/- 0.0006513722780898327</t>
-        </is>
-      </c>
-      <c r="BZ9" t="inlineStr">
-        <is>
-          <t>0.00016645859342493408 +/- 0.0006228310256802119</t>
-        </is>
-      </c>
-      <c r="CA9" t="inlineStr">
-        <is>
-          <t>0.0 +/- 0.0</t>
-        </is>
-      </c>
       <c r="CB9" t="inlineStr">
         <is>
-          <t>-0.0004577611319184105 +/- 0.0005409904286308814</t>
+          <t>0.0006658343736995365 +/- 0.0007718367453596114</t>
         </is>
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>0.0024552642530170864 +/- 0.001385836521460401</t>
+          <t>0.00258010819808574 +/- 0.0015769700642111106</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>-4.161464835622519e-05 +/- 0.00012484394506867558</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>-0.0014981273408239404 +/- 0.0005943760656298744</t>
+          <t>0.0 +/- 0.0007895824369958578</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>-0.0004577611319183883 +/- 0.0012267501434027029</t>
+          <t>-0.0014565126924677596 +/- 0.0014081501719258077</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>0.0013732833957553424 +/- 0.0015464755868549313</t>
+          <t>-0.003995006242197263 +/- 0.0010395335827546122</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
         <is>
-          <t>0.0006658343736995809 +/- 0.0008964069591568103</t>
+          <t>-0.0004577611319184327 +/- 0.0006297439013908354</t>
         </is>
       </c>
       <c r="CI9" t="inlineStr">
         <is>
-          <t>-0.005576362879733643 +/- 0.001179978932897022</t>
+          <t>0.0014981273408239738 +/- 0.0009155222638368795</t>
         </is>
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>-0.00166458593424883 +/- 0.0014888509213481897</t>
+          <t>0.0036204744069912587 +/- 0.0022336640699658363</t>
         </is>
       </c>
       <c r="CK9" t="inlineStr">
         <is>
-          <t>0.0021223470661673183 +/- 0.0007774257882758829</t>
+          <t>0.0017062005826050885 +/- 0.0006825309807264523</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>-0.0031493001555210286 +/- 0.0012227204660588424</t>
+          <t>0.0036158631415241006 +/- 0.001242344114204537</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4446,157 +4446,157 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>-0.004199066874028046 +/- 0.0014422423787707258</t>
+          <t>0.003460342146189732 +/- 0.0013630286269796156</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.016057542768273692 +/- 0.0007387247278382481</t>
+          <t>0.006454121306376371 +/- 0.0017230575276951992</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>0.001477449455676494 +/- 0.001601186647120855</t>
+          <t>-3.8880248833583764e-05 +/- 0.0012947765011933593</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>0.0033048211508553194 +/- 0.002398315787448077</t>
+          <t>0.002682737169517879 +/- 0.0020679760726239936</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>0.004976671850699809 +/- 0.0012753669880915149</t>
+          <t>0.005754276827371696 +/- 0.0015532647243731153</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.00015552099533437945 +/- 0.0002579023942733747</t>
+          <t>0.0 +/- 0.00017387775874805006</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>0.0012441679626749246 +/- 0.0016750123816903406</t>
+          <t>-0.004548989113530311 +/- 0.0007179698799618697</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>0.005909797822706031 +/- 0.0045534730861453675</t>
+          <t>0.012130637636080865 +/- 0.003415270801865897</t>
         </is>
       </c>
       <c r="L10" t="inlineStr">
         <is>
-          <t>0.0022939346811819304 +/- 0.002616556976421647</t>
+          <t>0.0030715396578538056 +/- 0.002968424882834593</t>
         </is>
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>0.0039657853810264095 +/- 0.0017715063374641779</t>
+          <t>0.003265940902021769 +/- 0.0018253024252418977</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>0.003888024883359231 +/- 0.0016768163804703</t>
+          <t>0.015357698289269061 +/- 0.0009874358553032868</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>0.01143079315707617 +/- 0.0019221161888504279</t>
+          <t>0.015357698289269051 +/- 0.001103130712217024</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>0.029665629860031063 +/- 0.0032531873477074356</t>
+          <t>0.03965785381026439 +/- 0.005336659389354132</t>
         </is>
       </c>
       <c r="Q10" t="inlineStr">
         <is>
-          <t>0.02962674961119748 +/- 0.003432930024050392</t>
+          <t>0.040163297045101076 +/- 0.0031493001555209887</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
         <is>
-          <t>0.000427682737169488 +/- 0.0019475085204304883</t>
+          <t>-0.002993779160186627 +/- 0.0013017627560484568</t>
         </is>
       </c>
       <c r="S10" t="inlineStr">
         <is>
-          <t>-0.002293934681181975 +/- 0.0011194541251079418</t>
+          <t>0.0034214618973561596 +/- 0.00193465867879079</t>
         </is>
       </c>
       <c r="T10" t="inlineStr">
         <is>
-          <t>0.0037713841368584356 +/- 0.002274079131553624</t>
+          <t>-0.0006609642301710683 +/- 0.001205287713841372</t>
         </is>
       </c>
       <c r="U10" t="inlineStr">
         <is>
-          <t>0.005443234836702926 +/- 0.0013011820008305849</t>
+          <t>0.002527216174183522 +/- 0.0013040831906102944</t>
         </is>
       </c>
       <c r="V10" t="inlineStr">
         <is>
-          <t>0.00015552099533432394 +/- 0.0003563433666372855</t>
+          <t>0.000544323483670317 +/- 0.00031104199066873673</t>
         </is>
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>0.026749611197511635 +/- 0.0029032900004035</t>
+          <t>0.012674961119751171 +/- 0.0025089060349769384</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>0.004432348367029515 +/- 0.0017230575276952027</t>
+          <t>0.0003888024883359154 +/- 0.001790181093813582</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>-0.0019440124416796657 +/- 0.001113360891390075</t>
+          <t>-0.0012830482115085528 +/- 0.0010146180677060711</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>-0.0017884914463452862 +/- 0.0010746714588713271</t>
+          <t>0.0017884914463452528 +/- 0.0012071675502535128</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.0018662519440124758 +/- 0.0016568643664589843</t>
+          <t>0.0038880248833592533 +/- 0.0018727207743067234</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>-0.0004665629860031606 +/- 0.0005714206242884562</t>
+          <t>0.0002721617418351641 +/- 0.0004276827371695435</t>
         </is>
       </c>
       <c r="AC10" t="inlineStr">
         <is>
-          <t>0.008009331259720032 +/- 0.002739333585351215</t>
+          <t>0.01224727838258165 +/- 0.002767061173974815</t>
         </is>
       </c>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>-0.01263608087091761 +/- 0.001976784419733481</t>
+          <t>-0.003071539657853817 +/- 0.0016260127267749966</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>-0.0026827371695179124 +/- 0.0014173970554866326</t>
+          <t>0.011119751166407477 +/- 0.0018253024252419194</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.008009331259720032 +/- 0.0018499809103219784</t>
+          <t>0.012947122861586313 +/- 0.0023653127798219354</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0005443234836702282 +/- 0.0003110419906687395</t>
+          <t>0.0010497667185069947 +/- 0.0008164852255054456</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.00015552099533443496 +/- 0.0007211211893853533</t>
+          <t>0.0016329704510109067 +/- 0.0005972897160084335</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
@@ -4606,122 +4606,122 @@
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>0.004082426127527195 +/- 0.0020591854862932173</t>
+          <t>0.007270606531881807 +/- 0.0013247842175272723</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>-0.0006609642301711127 +/- 0.002199742637607393</t>
+          <t>-0.005637636080870911 +/- 0.001705863994438608</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>0.000583203732503823 +/- 0.00039840399556607763</t>
+          <t>-0.0012052877138413632 +/- 0.00032296360275728766</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>-0.0010108864696734444 +/- 0.0005273973548308842</t>
+          <t>0.0017884914463452528 +/- 0.00043295212774730607</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>-0.001321928460342181 +/- 0.0016422015615818882</t>
+          <t>0.0008164852255054478 +/- 0.0011592575051225175</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>0.0034992223950232825 +/- 0.0013910220699843354</t>
+          <t>0.011780715396578535 +/- 0.0017129386292309946</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-0.0010886469673406119 +/- 0.0005714206242884457</t>
+          <t>-0.0004276827371695324 +/- 0.0004415947391757679</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-0.0022550544323484134 +/- 0.0012753669880915196</t>
+          <t>0.0012830482115085418 +/- 0.0018487548099484865</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>0.005676516329704473 +/- 0.0017578000863852827</t>
+          <t>0.005754276827371696 +/- 0.00083025491850943</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
         <is>
-          <t>0.0005443234836702615 +/- 0.0010018739289832928</t>
+          <t>0.012325038880248851 +/- 0.002409634592899867</t>
         </is>
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-0.009486780715396626 +/- 0.0018417914902530272</t>
+          <t>-0.003188180404354579 +/- 0.0021281387532510153</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>-0.003032659409020255 +/- 0.0017457188429738518</t>
+          <t>0.0018273716951788589 +/- 0.0015262664406213487</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>3.888024883356156e-05 +/- 0.0015103362830136049</t>
+          <t>0.0006609642301710683 +/- 0.0013915653318952773</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>0.0027604976671850245 +/- 0.0013959038157866377</t>
+          <t>-0.0010886469673405895 +/- 0.0012634585388236262</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>7.776049766714533e-05 +/- 0.0003809470828589454</t>
+          <t>0.0006998444790046632 +/- 0.0005158047885467008</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>0.0015163297045100665 +/- 0.001510336283013609</t>
+          <t>0.005093312597200606 +/- 0.0011058680134780744</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>-0.0049377916018662924 +/- 0.0019905016696998676</t>
+          <t>-0.0016718506998444794 +/- 0.0015845788392157792</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>0.0007387247278382136 +/- 0.0020825445942211514</t>
+          <t>-0.006726283048211501 +/- 0.002005633029009158</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>0.0066485225505442894 +/- 0.001235021786490563</t>
+          <t>0.006259720062208385 +/- 0.0019003653825583142</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-0.001321928460342181 +/- 0.000721121189385333</t>
+          <t>0.0004276827371695213 +/- 0.0007668383718240917</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>-0.00015552099533440168 +/- 0.0006998444790046471</t>
+          <t>-0.0006998444790046743 +/- 0.0004534177212165697</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
-          <t>-3.8880248833628175e-05 +/- 0.00044159473917574444</t>
+          <t>0.0 +/- 0.0</t>
         </is>
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>-0.0008553654743390648 +/- 0.0014317226002738637</t>
+          <t>0.008087091757387244 +/- 0.001996189370605521</t>
         </is>
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>-0.003071539657853839 +/- 0.001417397055486641</t>
+          <t>0.004354587869362358 +/- 0.0010830784041356198</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4731,92 +4731,92 @@
       </c>
       <c r="BI10" t="inlineStr">
         <is>
-          <t>-0.00046656298600314947 +/- 0.0006459272055146355</t>
+          <t>0.00027216174183515297 +/- 0.0004933350521170204</t>
         </is>
       </c>
       <c r="BJ10" t="inlineStr">
         <is>
-          <t>-0.0046267496111975556 +/- 0.0014490392809941226</t>
+          <t>0.002060653188180395 +/- 0.0014343597780479657</t>
         </is>
       </c>
       <c r="BK10" t="inlineStr">
         <is>
-          <t>-0.0007387247278383025 +/- 0.0018190804922689678</t>
+          <t>-0.003732503888024874 +/- 0.0027558390585799768</t>
         </is>
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>-0.0016718506998445015 +/- 0.0008702577482736864</t>
+          <t>-0.0008553654743390316 +/- 0.0008302549185094363</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>-0.0012441679626749914 +/- 0.0009805225671009853</t>
+          <t>0.003654743390357695 +/- 0.0008005933235604032</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>-0.003538102643856955 +/- 0.0017076354009329564</t>
+          <t>-0.012713841368584755 +/- 0.002035558337901768</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>0.020800933125971977 +/- 0.0017496111975116469</t>
+          <t>-0.005948678071539659 +/- 0.0014861209061910081</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>-0.000583203732503923 +/- 0.0008908584165932913</t>
+          <t>0.0028382581648522588 +/- 0.0013915653318952764</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>3.8880248833572664e-05 +/- 0.0002093765477112703</t>
+          <t>0.0004665629860031162 +/- 0.0005158047885467193</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>0.0038491446345256253 +/- 0.0017599487243788884</t>
+          <t>0.0005443234836702837 +/- 0.0011295364732763543</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.004082426127527195 +/- 0.0019844168204004396</t>
+          <t>0.002216174183514774 +/- 0.0009531610164954326</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.0003499222395022761 +/- 0.0008771783960092226</t>
+          <t>0.0005832037325038675 +/- 0.0010175934936471661</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>0.004626749611197478 +/- 0.0024246441411615687</t>
+          <t>0.0006998444790046743 +/- 0.0011241704739347403</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>0.0001944012441679077 +/- 0.001089341036245853</t>
+          <t>0.0008553654743390204 +/- 0.001355800604522756</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
         <is>
-          <t>-0.000544323483670317 +/- 0.0019455670300461546</t>
+          <t>-0.0019440124416796323 +/- 0.0014232507945352389</t>
         </is>
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>7.776049766715643e-05 +/- 0.00033895015113066703</t>
+          <t>7.776049766718973e-05 +/- 0.0002332814930015692</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>-3.8880248833639275e-05 +/- 0.0010921129008699918</t>
+          <t>-0.00034992223950234267 +/- 0.0006135199781516285</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>0.0006998444790046077 +/- 0.00038094708285897264</t>
+          <t>-7.776049766720084e-05 +/- 0.0005158047885467227</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="CB10" t="inlineStr">
         <is>
-          <t>-0.00031104199066879225 +/- 0.0006689210938602277</t>
+          <t>-0.0002332814930015692 +/- 0.0005553210286581088</t>
         </is>
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>-0.0012830482115085639 +/- 0.0008527104276617973</t>
+          <t>0.004432348367029548 +/- 0.0010746714588713406</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
@@ -4841,37 +4841,37 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>0.0007776049766717974 +/- 0.0007968079911321824</t>
+          <t>0.0006609642301710905 +/- 0.00046167737507922876</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>0.003421461897356093 +/- 0.001275366988091513</t>
+          <t>0.0002332814930015692 +/- 0.0010886469673405928</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>0.0034214618973561262 +/- 0.0011767298561758679</t>
+          <t>-7.776049766718973e-05 +/- 0.0010547947096618017</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
         <is>
-          <t>-0.0006998444790047187 +/- 0.0006689210938602187</t>
+          <t>-0.00042768273716954354 +/- 0.00020937654771130743</t>
         </is>
       </c>
       <c r="CI10" t="inlineStr">
         <is>
-          <t>0.0015552099533436615 +/- 0.0010286746932599525</t>
+          <t>-0.0021384136858475953 +/- 0.0015083331836136004</t>
         </is>
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>0.0012441679626749135 +/- 0.0009331259720062222</t>
+          <t>0.0004276827371695102 +/- 0.0012830482115085676</t>
         </is>
       </c>
       <c r="CK10" t="inlineStr">
         <is>
-          <t>0.0017496111975116135 +/- 0.0011302054318622567</t>
+          <t>0.0006998444790046743 +/- 0.001214657803406955</t>
         </is>
       </c>
     </row>
@@ -4881,7 +4881,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>3.915426781521125e-05 +/- 0.0013272083991134225</t>
+          <t>-0.005168363351605332 +/- 0.0014311407112370523</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4891,157 +4891,157 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>-0.025176194205168333 +/- 0.0036396624626811717</t>
+          <t>-0.003093187157400157 +/- 0.0033747708272148028</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>-0.010649960845732175 +/- 0.002425037207079411</t>
+          <t>-0.009827721221613161 +/- 0.0015607777155829858</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>-0.01033672670321063 +/- 0.002998306925462291</t>
+          <t>0.003837118245888804 +/- 0.0012356878494956497</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>-0.025763508222396238 +/- 0.0027396798252992995</t>
+          <t>-0.015074393108848871 +/- 0.0019121559040054465</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>0.001018010963194993 +/- 0.001508328918109505</t>
+          <t>0.0016053249804228841 +/- 0.0018066205160625485</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-3.9154267815177944e-05 +/- 0.00040878255712256743</t>
+          <t>-0.0003132341425215457 +/- 0.0004217043701749979</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>0.005168363351605376 +/- 0.0014733663055776754</t>
+          <t>0.0009397024275646038 +/- 0.00210997550278896</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>-0.004111198120595116 +/- 0.005042394785502682</t>
+          <t>0.005129209083790132 +/- 0.0031685940495199973</t>
         </is>
       </c>
       <c r="L11" t="inlineStr">
         <is>
-          <t>-0.013586530931871565 +/- 0.004374251996024277</t>
+          <t>0.01162881754111198 +/- 0.002701644479248217</t>
         </is>
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>0.007008613938919372 +/- 0.00264080951118514</t>
+          <t>-0.003915426781519205 +/- 0.0012381666641223016</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>-0.02615505090054814 +/- 0.002642840568627447</t>
+          <t>-0.012294440093970248 +/- 0.0023177210003051864</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>-0.020281910728269337 +/- 0.003647026162003128</t>
+          <t>-0.0019577133907596076 +/- 0.002151704254351447</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>0.008026624902114355 +/- 0.003776915736838437</t>
+          <t>-0.003641346906812837 +/- 0.003515390442486711</t>
         </is>
       </c>
       <c r="Q11" t="inlineStr">
         <is>
-          <t>0.017971808927173073 +/- 0.002067775399610153</t>
+          <t>0.008888018794048557 +/- 0.002215245913831745</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
         <is>
-          <t>-0.00011746280344555604 +/- 0.0018117048240030213</t>
+          <t>0.006068911511354758 +/- 0.0032441384317114176</t>
         </is>
       </c>
       <c r="S11" t="inlineStr">
         <is>
-          <t>-0.009201252936570047 +/- 0.0024152185612045535</t>
+          <t>0.0008222396241190477 +/- 0.002082550688640906</t>
         </is>
       </c>
       <c r="T11" t="inlineStr">
         <is>
-          <t>-0.0021143304620203527 +/- 0.00127717356541113</t>
+          <t>-0.0015270164447924728 +/- 0.0025702025735749793</t>
         </is>
       </c>
       <c r="U11" t="inlineStr">
         <is>
-          <t>0.000469851213782313 +/- 0.0009874330628753675</t>
+          <t>0.0029365700861394006 +/- 0.00248405981606295</t>
         </is>
       </c>
       <c r="V11" t="inlineStr">
         <is>
-          <t>1.1102230246251566e-17 +/- 0.00035020641777600437</t>
+          <t>7.83085356303781e-05 +/- 0.0001566170712607562</t>
         </is>
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>0.0031323414252153793 +/- 0.0025794313378231224</t>
+          <t>-0.003288958496476135 +/- 0.0023177210003052177</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>0.0028191072826938223 +/- 0.0016313756191072809</t>
+          <t>-0.0035630383711824478 +/- 0.002259102856186633</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>0.0033672670321065025 +/- 0.00160675681508875</t>
+          <t>-0.0013703993735317056 +/- 0.0011246207217184986</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>0.001487862176977306 +/- 0.0013540811641182947</t>
+          <t>0.0007439310884886585 +/- 0.0019455377053727249</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.0016836335160532734 +/- 0.0016243123345882086</t>
+          <t>0.0027407987470634554 +/- 0.00204953051343812</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>-3.9154267815166845e-05 +/- 0.0006656225528582542</t>
+          <t>0.002270947533281131 +/- 0.0006736354946783544</t>
         </is>
       </c>
       <c r="AC11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0021870383780374205</t>
+          <t>-0.004267815191855928 +/- 0.001154221062880464</t>
         </is>
       </c>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>-0.0010571652310101486 +/- 0.0014230839346426156</t>
+          <t>0.008809710258418157 +/- 0.002389693738397357</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>0.001957713390759619 +/- 0.0013563436237814348</t>
+          <t>0.0082223962411903 +/- 0.0023880893785398444</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0028582615505090337 +/- 0.0014550433967159087</t>
+          <t>0.0040328895849647715 +/- 0.0025618383403219263</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>-0.0014878621769772726 +/- 0.0008361063627275893</t>
+          <t>-0.0003132341425215346 +/- 0.0007985935025204259</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.0015661707126076619 +/- 0.0013103524299672342</t>
+          <t>0.0011354737666405934 +/- 0.0007101940934697523</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
@@ -5051,122 +5051,122 @@
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>-0.013077525450274042 +/- 0.0023765060149559176</t>
+          <t>0.0003132341425215346 +/- 0.0022884321372282856</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>0.005403288958496499 +/- 0.002040534725261627</t>
+          <t>0.010806577916992965 +/- 0.0016351302284903038</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>3.915426781521125e-05 +/- 0.00064217773950106</t>
+          <t>0.0007047768206734584 +/- 0.0009064868365536466</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>-0.0010571652310101599 +/- 0.0009107050391239478</t>
+          <t>0.0016444792482380732 +/- 0.0010329605292304558</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>0.005755677368833223 +/- 0.0016148465643932163</t>
+          <t>0.0044244322631166845 +/- 0.0016523843262340615</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>0.004032889584964794 +/- 0.0019025106676987282</t>
+          <t>0.008026624902114343 +/- 0.0025630349019660297</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-0.00043069694596709063 +/- 0.0005925115877220737</t>
+          <t>0.002036021926389997 +/- 0.0008361063627275966</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-0.00395458104933436 +/- 0.0015509242224227458</t>
+          <t>0.007400156617071274 +/- 0.0022110897264675865</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>0.00027407987470636776 +/- 0.002585664366656076</t>
+          <t>0.002701644479248244 +/- 0.001710732362956421</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
         <is>
-          <t>-0.0013312451057165054 +/- 0.0013009591014750321</t>
+          <t>-0.007321848081440896 +/- 0.0021520604672922903</t>
         </is>
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-0.004306969459671084 +/- 0.0028125740009503253</t>
+          <t>-0.002623335943617866 +/- 0.00254382237600325</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>0.0002349256068911565 +/- 0.0015385186142825814</t>
+          <t>0.003993735317149583 +/- 0.0021573966035952955</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>-0.005559906029757223 +/- 0.001554380050217645</t>
+          <t>0.0023101018010963314 +/- 0.0009005481597494138</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>-0.005090054815974909 +/- 0.002426301234898926</t>
+          <t>0.0012529365700861272 +/- 0.0018180402139771328</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>0.00011746280344557825 +/- 0.0005551075520265524</t>
+          <t>0.00035238841033674584 +/- 0.0005090054815975037</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>-0.004894283476898975 +/- 0.003069305026979807</t>
+          <t>0.0034064212999217135 +/- 0.0015169436670172574</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>-0.005442443226311644 +/- 0.0016653226560796076</t>
+          <t>-0.011198120595144866 +/- 0.0019197573488067645</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-0.009671104150352373 +/- 0.000927386004880761</t>
+          <t>-0.014722004698512148 +/- 0.002650949237245245</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-0.0007439310884886363 +/- 0.0018402505873140044</t>
+          <t>-0.0011354737666405602 +/- 0.0017017473619499474</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>0.0016836335160532623 +/- 0.00043069694596711383</t>
+          <t>0.0010963194988253932 +/- 0.0008894139930775769</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>-0.000587314017227869 +/- 0.0005606038004415198</t>
+          <t>0.0003132341425215457 +/- 0.0007177095841747723</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
-          <t>7.83085356303892e-05 +/- 0.00045661330421653106</t>
+          <t>-0.0017619420516836626 +/- 0.0006373853013351511</t>
         </is>
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>0.0012529365700861606 +/- 0.001564211774114184</t>
+          <t>-0.010649960845732187 +/- 0.0022884321372282643</t>
         </is>
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>-0.008731401722787756 +/- 0.0018032230132606726</t>
+          <t>-0.014604541895066558 +/- 0.0016337232611609233</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5176,147 +5176,147 @@
       </c>
       <c r="BI11" t="inlineStr">
         <is>
-          <t>0.0007439310884886585 +/- 0.0011136619149042873</t>
+          <t>0.0008613938919342368 +/- 0.0005194400611363291</t>
         </is>
       </c>
       <c r="BJ11" t="inlineStr">
         <is>
-          <t>-0.00681284259984336 +/- 0.0021814233793553783</t>
+          <t>0.0018010963194988404 +/- 0.000993623926425173</t>
         </is>
       </c>
       <c r="BK11" t="inlineStr">
         <is>
-          <t>-0.0025841816758026435 +/- 0.001735201237757276</t>
+          <t>-0.015191855912294439 +/- 0.0030670565430800578</t>
         </is>
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>-0.0013312451057165275 +/- 0.0007672638191959819</t>
+          <t>-0.0013703993735317277 +/- 0.0007682622110551365</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>-0.0028191072826938 +/- 0.0023150736881902183</t>
+          <t>0.003915426781519182 +/- 0.0026207048599344467</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>-0.00391542678151916 +/- 0.0014439380512596583</t>
+          <t>-0.00356303837118247 +/- 0.0023716629163520594</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>0.002153484729835564 +/- 0.0028464371759868313</t>
+          <t>0.0045027407987470736 +/- 0.002520817322289718</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>-0.00019577133907595635 +/- 0.002370369752179371</t>
+          <t>-0.0001566170712607673 +/- 0.0019826137668241613</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>0.00043069694596710174 +/- 0.00044470699653878943</t>
+          <t>0.0005090054815974799 +/- 0.0002507096412464155</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>0.000509005481597502 +/- 0.002501280540905946</t>
+          <t>0.0033281127642913024 +/- 0.0023114286833430743</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.002584181675802677 +/- 0.0018630191469648227</t>
+          <t>-0.0013703993735317166 +/- 0.0010542609254374485</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>-0.004072043852779927 +/- 0.0010963194988253902</t>
+          <t>-0.0033281127642913132 +/- 0.0010829535384447428</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>-0.0012529365700861272 +/- 0.002070368686985469</t>
+          <t>0.005951448707909179 +/- 0.001308010421964769</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>-0.0030931871574001344 +/- 0.002515947349478043</t>
+          <t>0.00532498042286611 +/- 0.002691126120194132</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
         <is>
-          <t>0.001605324980422873 +/- 0.0022591028561866214</t>
+          <t>0.003915426781519194 +/- 0.00259129085478065</t>
         </is>
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>0.0003915426781519127 +/- 0.0002476333328244793</t>
+          <t>0.0005873140172278802 +/- 0.0002626548133320343</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>-0.00168363351605324 +/- 0.0009913068834120845</t>
+          <t>-0.0015270164447924838 +/- 0.000772242870920759</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>0.0015270164447925062 +/- 0.0012313379164852307</t>
+          <t>0.0007830853563038365 +/- 0.0009590797739949788</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
         <is>
-          <t>0.0 +/- 0.0</t>
+          <t>7.83085356303781e-05 +/- 0.0001566170712607562</t>
         </is>
       </c>
       <c r="CB11" t="inlineStr">
         <is>
-          <t>0.002545027407987488 +/- 0.0004714798190599898</t>
+          <t>0.0027407987470634333 +/- 0.0006313435981439633</t>
         </is>
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>-0.012803445575567729 +/- 0.001506803555590746</t>
+          <t>-0.0014878621769772948 +/- 0.0015933429874217574</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>0.00011746280344556714 +/- 0.00025070964124637387</t>
+          <t>-0.0001566170712607673 +/- 0.00025972003056816786</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>-0.002819107282693789 +/- 0.0010622286582811621</t>
+          <t>0.0033672670321065246 +/- 0.0009462056361467942</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>0.00254502740798751 +/- 0.0026742680213828122</t>
+          <t>0.0016836335160532623 +/- 0.0017861385635014823</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>0.00595144870790919 +/- 0.0035662639112719573</t>
+          <t>0.00814408770555991 +/- 0.0014524069687542477</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
         <is>
-          <t>-0.007321848081440851 +/- 0.001094219938330635</t>
+          <t>-0.0007439310884886474 +/- 0.0018319009499278892</t>
         </is>
       </c>
       <c r="CI11" t="inlineStr">
         <is>
-          <t>-0.0050117462803445315 +/- 0.0019004950821474712</t>
+          <t>0.003993735317149583 +/- 0.001659328120627807</t>
         </is>
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>-0.00336726703210648 +/- 0.0031818715197979514</t>
+          <t>0.009162098668754903 +/- 0.0037276837072550886</t>
         </is>
       </c>
       <c r="CK11" t="inlineStr">
         <is>
-          <t>-0.007517619420516808 +/- 0.0019085446526160964</t>
+          <t>0.003954581049334394 +/- 0.0023781181893594624</t>
         </is>
       </c>
     </row>
